--- a/public/fa/example-project.xlsx
+++ b/public/fa/example-project.xlsx
@@ -8,12 +8,17 @@
     <sheet name="Business Rules" sheetId="3" r:id="rId3"/>
     <sheet name="Actors" sheetId="4" r:id="rId4"/>
     <sheet name="Process Steps" sheetId="5" r:id="rId5"/>
-    <sheet name="Diagrams" sheetId="6" r:id="rId6"/>
-    <sheet name="Wireframes" sheetId="7" r:id="rId7"/>
-    <sheet name="API Endpoints" sheetId="8" r:id="rId8"/>
-    <sheet name="SQL Validations" sheetId="9" r:id="rId9"/>
-    <sheet name="Test Cases" sheetId="10" r:id="rId10"/>
-    <sheet name="Documents" sheetId="11" r:id="rId11"/>
+    <sheet name="Spec Sections" sheetId="6" r:id="rId6"/>
+    <sheet name="Spec Fields" sheetId="7" r:id="rId7"/>
+    <sheet name="Spec Validations" sheetId="8" r:id="rId8"/>
+    <sheet name="Spec Errors" sheetId="9" r:id="rId9"/>
+    <sheet name="Spec Edge Cases" sheetId="10" r:id="rId10"/>
+    <sheet name="Diagrams" sheetId="11" r:id="rId11"/>
+    <sheet name="Wireframes" sheetId="12" r:id="rId12"/>
+    <sheet name="API Endpoints" sheetId="13" r:id="rId13"/>
+    <sheet name="SQL Validations" sheetId="14" r:id="rId14"/>
+    <sheet name="Test Cases" sheetId="15" r:id="rId15"/>
+    <sheet name="Documents" sheetId="16" r:id="rId16"/>
   </sheets>
 </workbook>
 </file>
@@ -670,1248 +675,120 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:D7"/>
   <cols>
     <col min="1" max="1" width="26.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
     <col min="3" max="3" width="26.83203125" customWidth="1"/>
     <col min="4" max="4" width="26.83203125" customWidth="1"/>
-    <col min="5" max="5" width="26.83203125" customWidth="1"/>
-    <col min="6" max="6" width="26.83203125" customWidth="1"/>
-    <col min="7" max="7" width="26.83203125" customWidth="1"/>
-    <col min="8" max="8" width="26.83203125" customWidth="1"/>
-    <col min="9" max="9" width="26.83203125" customWidth="1"/>
-    <col min="10" max="10" width="26.83203125" customWidth="1"/>
-    <col min="11" max="11" width="26.83203125" customWidth="1"/>
-    <col min="12" max="12" width="26.83203125" customWidth="1"/>
-    <col min="13" max="13" width="26.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>Section</v>
+      </c>
+      <c r="B1" t="str">
         <v>ID</v>
       </c>
-      <c r="B1" t="str">
+      <c r="C1" t="str">
         <v>Scenario</v>
       </c>
-      <c r="C1" t="str">
-        <v>Suite</v>
-      </c>
       <c r="D1" t="str">
-        <v>Preconditions</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Steps</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Expected Result</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Status</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Priority</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Type</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Requirement</v>
-      </c>
-      <c r="K1" t="str">
-        <v>Last Run</v>
-      </c>
-      <c r="L1" t="str">
-        <v>Executed By</v>
-      </c>
-      <c r="M1" t="str">
-        <v>Defect</v>
-      </c>
-    </row>
-    <row r="2" xml:space="preserve">
+        <v>Expected Behaviour</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" t="str">
-        <v>TC-001</v>
+        <v>FS-001</v>
       </c>
       <c r="B2" t="str">
-        <v>A settled transaction inside the window can be disputed</v>
+        <v>EC-001</v>
       </c>
       <c r="C2" t="str">
-        <v>Disputes</v>
+        <v>The transaction settles while the cardholder is on the screen</v>
       </c>
       <c r="D2" t="str">
-        <v>A card with a settled transaction dated 30 days ago</v>
-      </c>
-      <c r="E2" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Open the transaction -&gt; the Dispute action is available
-2. Choose a reason and confirm -&gt; a reference is shown</v>
-      </c>
-      <c r="F2" t="str">
-        <v>The dispute exists with the status Submitted.</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Critical</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Functional</v>
-      </c>
-      <c r="J2" t="str">
-        <v>BR-001</v>
-      </c>
-      <c r="K2" t="str">
-        <v>2026-02-19</v>
-      </c>
-      <c r="L2" t="str">
-        <v>Saadaoui Abdessalem</v>
+        <v>The Dispute action becomes available without a reload; no error is shown for the earlier state.</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>TC-002</v>
+        <v>FS-001</v>
       </c>
       <c r="B3" t="str">
-        <v>A transaction older than 120 days cannot be disputed</v>
+        <v>EC-002</v>
       </c>
       <c r="C3" t="str">
-        <v>Disputes</v>
+        <v>The dispute is submitted on day 120 at 23:59 local time</v>
       </c>
       <c r="D3" t="str">
-        <v>A card with a settled transaction dated 130 days ago</v>
-      </c>
-      <c r="E3" t="str">
-        <v>1. Open the transaction -&gt; the Dispute action is disabled and the reason is shown</v>
-      </c>
-      <c r="F3" t="str">
-        <v>No dispute is created and the cardholder is told why.</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Critical</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Negative</v>
-      </c>
-      <c r="J3" t="str">
-        <v>BR-001</v>
-      </c>
-      <c r="K3" t="str">
-        <v>2026-02-19</v>
-      </c>
-      <c r="L3" t="str">
-        <v>Saadaoui Abdessalem</v>
-      </c>
-    </row>
-    <row r="4" xml:space="preserve">
+        <v>It is accepted; the window is counted in whole days against the settlement date, not in hours.</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" t="str">
-        <v>TC-003</v>
+        <v>FS-001</v>
       </c>
       <c r="B4" t="str">
-        <v>A provisional credit is posted for the disputed amount</v>
+        <v>EC-003</v>
       </c>
       <c r="C4" t="str">
-        <v>Settlement</v>
+        <v>The cardholder taps Submit twice</v>
       </c>
       <c r="D4" t="str">
-        <v>A dispute of 84.50 accepted before the end-of-day run</v>
-      </c>
-      <c r="E4" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Run end of day -&gt; a posting appears
-2. Read the posting -&gt; the amount is 84.50</v>
-      </c>
-      <c r="F4" t="str">
-        <v>One provisional credit of 84.50 and no second posting.</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Critical</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Integration</v>
-      </c>
-      <c r="J4" t="str">
-        <v>BR-002</v>
-      </c>
-      <c r="K4" t="str">
-        <v>2026-02-20</v>
-      </c>
-      <c r="L4" t="str">
-        <v>Saadaoui Abdessalem</v>
+        <v>One dispute is created; the second call returns the same reference.</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>TC-004</v>
+        <v>FS-002</v>
       </c>
       <c r="B5" t="str">
-        <v>The sixth evidence file is refused</v>
+        <v>EC-004</v>
       </c>
       <c r="C5" t="str">
-        <v>Evidence</v>
+        <v>The account is closed before the provisional credit posts</v>
       </c>
       <c r="D5" t="str">
-        <v>A dispute Under Review with five files attached</v>
-      </c>
-      <c r="E5" t="str">
-        <v>1. Attach a sixth file -&gt; the error ATTACHMENT_LIMIT is shown</v>
-      </c>
-      <c r="F5" t="str">
-        <v>The file is refused and the five existing files are untouched.</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Failed</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="I5" t="str">
-        <v>Negative</v>
-      </c>
-      <c r="J5" t="str">
-        <v>BR-003</v>
-      </c>
-      <c r="K5" t="str">
-        <v>2026-02-20</v>
-      </c>
-      <c r="L5" t="str">
-        <v>Saadaoui Abdessalem</v>
-      </c>
-      <c r="M5" t="str">
-        <v>DEF-118</v>
+        <v>The credit is held and an operations task is raised; the case continues regardless.</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>TC-005</v>
+        <v>FS-002</v>
       </c>
       <c r="B6" t="str">
-        <v>One notification per status change</v>
+        <v>EC-005</v>
       </c>
       <c r="C6" t="str">
-        <v>Notifications</v>
+        <v>The transaction is refunded by the merchant while the case is open</v>
       </c>
       <c r="D6" t="str">
-        <v>A dispute with the status Submitted</v>
-      </c>
-      <c r="E6" t="str">
-        <v>1. Move it to Under Review -&gt; one notification is sent</v>
-      </c>
-      <c r="F6" t="str">
-        <v>Exactly one notification, not one per retry.</v>
-      </c>
-      <c r="G6" t="str">
-        <v>Not Run</v>
-      </c>
-      <c r="H6" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="I6" t="str">
-        <v>Functional</v>
-      </c>
-      <c r="J6" t="str">
-        <v>BR-004</v>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v/>
+        <v>The provisional credit is reversed and the case is closed as Resolved, with one notification only.</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>FS-003</v>
+      </c>
+      <c r="B7" t="str">
+        <v>EC-006</v>
+      </c>
+      <c r="C7" t="str">
+        <v>The case moves to Resolved while a file is uploading</v>
+      </c>
+      <c r="D7" t="str">
+        <v>The upload completes and is stored, but no further file is accepted.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D7"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
-  <cols>
-    <col min="1" max="1" width="26.83203125" customWidth="1"/>
-    <col min="2" max="2" width="26.83203125" customWidth="1"/>
-    <col min="3" max="3" width="26.83203125" customWidth="1"/>
-    <col min="4" max="4" width="26.83203125" customWidth="1"/>
-    <col min="5" max="5" width="26.83203125" customWidth="1"/>
-    <col min="6" max="6" width="26.83203125" customWidth="1"/>
-    <col min="7" max="7" width="26.83203125" customWidth="1"/>
-    <col min="8" max="8" width="26.83203125" customWidth="1"/>
-    <col min="9" max="9" width="26.83203125" customWidth="1"/>
-    <col min="10" max="10" width="26.83203125" customWidth="1"/>
-    <col min="11" max="11" width="26.83203125" customWidth="1"/>
-    <col min="12" max="12" width="26.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>ID</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Name</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Format</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Description</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Category</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Version</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Author</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Last Updated</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Size</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Status</v>
-      </c>
-      <c r="K1" t="str">
-        <v>Confidentiality</v>
-      </c>
-      <c r="L1" t="str">
-        <v>Requirements</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>DOC-001</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Card disputes — business requirements</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Word</v>
-      </c>
-      <c r="D2" t="str">
-        <v>The signed requirements pack behind BR-001 and BR-002.</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Requirements</v>
-      </c>
-      <c r="F2" t="str">
-        <v>1.2</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Saadaoui Abdessalem</v>
-      </c>
-      <c r="H2" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="I2" t="str">
-        <v>412 KB</v>
-      </c>
-      <c r="J2" t="str">
-        <v>Approved</v>
-      </c>
-      <c r="K2" t="str">
-        <v>Internal</v>
-      </c>
-      <c r="L2" t="str">
-        <v>BR-001, BR-002</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>DOC-002</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Disputes API contract</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Swagger</v>
-      </c>
-      <c r="D3" t="str">
-        <v>OpenAPI 3.1 definition of the four dispute endpoints.</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Interface</v>
-      </c>
-      <c r="F3" t="str">
-        <v>1.0.0</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Saadaoui Abdessalem</v>
-      </c>
-      <c r="H3" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="I3" t="str">
-        <v>38 KB</v>
-      </c>
-      <c r="J3" t="str">
-        <v>In Review</v>
-      </c>
-      <c r="K3" t="str">
-        <v>Internal</v>
-      </c>
-      <c r="L3" t="str">
-        <v>BR-001, BR-003</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>DOC-003</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Dispute process model</v>
-      </c>
-      <c r="C4" t="str">
-        <v>BPMN</v>
-      </c>
-      <c r="D4" t="str">
-        <v>The BPMN 2.0 file behind the process flow.</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Process</v>
-      </c>
-      <c r="F4" t="str">
-        <v>1.0</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Saadaoui Abdessalem</v>
-      </c>
-      <c r="H4" t="str">
-        <v>2026-02-14</v>
-      </c>
-      <c r="I4" t="str">
-        <v>24 KB</v>
-      </c>
-      <c r="J4" t="str">
-        <v>Approved</v>
-      </c>
-      <c r="K4" t="str">
-        <v>Internal</v>
-      </c>
-      <c r="L4" t="str">
-        <v>BR-001</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E8"/>
-  <cols>
-    <col min="1" max="1" width="26.83203125" customWidth="1"/>
-    <col min="2" max="2" width="26.83203125" customWidth="1"/>
-    <col min="3" max="3" width="26.83203125" customWidth="1"/>
-    <col min="4" max="4" width="26.83203125" customWidth="1"/>
-    <col min="5" max="5" width="26.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>ID</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Requirement</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Given</v>
-      </c>
-      <c r="D1" t="str">
-        <v>When</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Then</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>AC-001.1</v>
-      </c>
-      <c r="B2" t="str">
-        <v>BR-001</v>
-      </c>
-      <c r="C2" t="str">
-        <v>a settled card transaction dated within the last 120 days</v>
-      </c>
-      <c r="D2" t="str">
-        <v>the cardholder raises a dispute and selects a reason code</v>
-      </c>
-      <c r="E2" t="str">
-        <v>the dispute is created with the status Submitted and a reference is shown</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>AC-001.2</v>
-      </c>
-      <c r="B3" t="str">
-        <v>BR-001</v>
-      </c>
-      <c r="C3" t="str">
-        <v>a transaction older than 120 days</v>
-      </c>
-      <c r="D3" t="str">
-        <v>the cardholder opens it</v>
-      </c>
-      <c r="E3" t="str">
-        <v>the dispute action is unavailable and the reason is stated on screen</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>AC-001.3</v>
-      </c>
-      <c r="B4" t="str">
-        <v>BR-001</v>
-      </c>
-      <c r="C4" t="str">
-        <v>a transaction that already has an open dispute</v>
-      </c>
-      <c r="D4" t="str">
-        <v>the cardholder tries to dispute it again</v>
-      </c>
-      <c r="E4" t="str">
-        <v>the existing case is shown instead of a second one being created</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>AC-002.1</v>
-      </c>
-      <c r="B5" t="str">
-        <v>BR-002</v>
-      </c>
-      <c r="C5" t="str">
-        <v>a dispute accepted at 16:00 on a working day</v>
-      </c>
-      <c r="D5" t="str">
-        <v>the next end-of-day run completes</v>
-      </c>
-      <c r="E5" t="str">
-        <v>a provisional credit for the full disputed amount is posted</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>AC-002.2</v>
-      </c>
-      <c r="B6" t="str">
-        <v>BR-002</v>
-      </c>
-      <c r="C6" t="str">
-        <v>a dispute later rejected</v>
-      </c>
-      <c r="D6" t="str">
-        <v>the rejection is recorded</v>
-      </c>
-      <c r="E6" t="str">
-        <v>the provisional credit is reversed and the cardholder is told why</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>AC-003.1</v>
-      </c>
-      <c r="B7" t="str">
-        <v>BR-003</v>
-      </c>
-      <c r="C7" t="str">
-        <v>a dispute with the status Under Review and four files already attached</v>
-      </c>
-      <c r="D7" t="str">
-        <v>the cardholder attaches a fifth file of 8 MB</v>
-      </c>
-      <c r="E7" t="str">
-        <v>the file is accepted and the attach action is then disabled</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>AC-004.1</v>
-      </c>
-      <c r="B8" t="str">
-        <v>BR-004</v>
-      </c>
-      <c r="C8" t="str">
-        <v>a dispute that moves from Submitted to Under Review</v>
-      </c>
-      <c r="D8" t="str">
-        <v>the status change is saved</v>
-      </c>
-      <c r="E8" t="str">
-        <v>exactly one notification is sent to the cardholder</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E8"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J5"/>
-  <cols>
-    <col min="1" max="1" width="26.83203125" customWidth="1"/>
-    <col min="2" max="2" width="26.83203125" customWidth="1"/>
-    <col min="3" max="3" width="26.83203125" customWidth="1"/>
-    <col min="4" max="4" width="26.83203125" customWidth="1"/>
-    <col min="5" max="5" width="26.83203125" customWidth="1"/>
-    <col min="6" max="6" width="26.83203125" customWidth="1"/>
-    <col min="7" max="7" width="26.83203125" customWidth="1"/>
-    <col min="8" max="8" width="26.83203125" customWidth="1"/>
-    <col min="9" max="9" width="26.83203125" customWidth="1"/>
-    <col min="10" max="10" width="26.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>ID</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Description</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Logic</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Priority</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Source</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Status</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Category</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Owner</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Effective From</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Requirements</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>RULE-001</v>
-      </c>
-      <c r="B2" t="str">
-        <v>A dispute may only be raised against a settled transaction.</v>
-      </c>
-      <c r="C2" t="str">
-        <v>IF transaction.status &lt;&gt; 'SETTLED' THEN reject WITH 'NOT_DISPUTABLE'</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Critical</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Scheme rules, chapter 11</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Approved</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Eligibility</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Saadaoui Abdessalem</v>
-      </c>
-      <c r="I2" t="str">
-        <v>2026-01-01</v>
-      </c>
-      <c r="J2" t="str">
-        <v>BR-001</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>RULE-002</v>
-      </c>
-      <c r="B3" t="str">
-        <v>A transaction is disputable for 120 days after its settlement date.</v>
-      </c>
-      <c r="C3" t="str">
-        <v>IF today - transaction.settled_date &gt; 120 THEN reject WITH 'WINDOW_CLOSED'</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Critical</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Scheme rules, chapter 11</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Approved</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Eligibility</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Saadaoui Abdessalem</v>
-      </c>
-      <c r="I3" t="str">
-        <v>2026-01-01</v>
-      </c>
-      <c r="J3" t="str">
-        <v>BR-001</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>RULE-003</v>
-      </c>
-      <c r="B4" t="str">
-        <v>A provisional credit equals the disputed amount, never more.</v>
-      </c>
-      <c r="C4" t="str">
-        <v>credit.amount = dispute.amount AND credit.amount &lt;= transaction.amount</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Critical</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Treasury policy 7.1</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Approved</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Settlement</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Saadaoui Abdessalem</v>
-      </c>
-      <c r="I4" t="str">
-        <v>2026-01-01</v>
-      </c>
-      <c r="J4" t="str">
-        <v>BR-002</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>RULE-004</v>
-      </c>
-      <c r="B5" t="str">
-        <v>At most five evidence files, each at most 10 MB, per dispute.</v>
-      </c>
-      <c r="C5" t="str">
-        <v>IF files.count &gt; 5 OR file.size &gt; 10485760 THEN reject WITH 'ATTACHMENT_LIMIT'</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Operations handbook 3.4</v>
-      </c>
-      <c r="F5" t="str">
-        <v>In Review</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Evidence</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Saadaoui Abdessalem</v>
-      </c>
-      <c r="I5" t="str">
-        <v>2026-03-01</v>
-      </c>
-      <c r="J5" t="str">
-        <v>BR-003</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J5"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
-  <cols>
-    <col min="1" max="1" width="26.83203125" customWidth="1"/>
-    <col min="2" max="2" width="26.83203125" customWidth="1"/>
-    <col min="3" max="3" width="26.83203125" customWidth="1"/>
-    <col min="4" max="4" width="26.83203125" customWidth="1"/>
-    <col min="5" max="5" width="26.83203125" customWidth="1"/>
-    <col min="6" max="6" width="26.83203125" customWidth="1"/>
-    <col min="7" max="7" width="26.83203125" customWidth="1"/>
-    <col min="8" max="8" width="26.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>ID</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Name</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Type</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Description</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Responsibilities</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Permissions</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Systems</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Channel</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>ACT-001</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Cardholder</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Human</v>
-      </c>
-      <c r="D2" t="str">
-        <v>The retail customer whose card was charged.</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Raises the dispute; supplies evidence; accepts the outcome</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Read own transactions; create dispute; attach evidence</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Mobile app; internet banking</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Mobile</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>ACT-002</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Disputes agent</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Human</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Back-office analyst who investigates the case against the scheme rules.</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Reviews evidence; decides the outcome; raises the chargeback</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Read all disputes; change status; post adjustments</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Disputes console; card management system</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Back Office</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>ACT-003</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Card scheme</v>
-      </c>
-      <c r="C4" t="str">
-        <v>External</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Visa or Mastercard, which arbitrates the chargeback.</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Accepts the chargeback; rules on representment</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Receive chargeback messages</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Scheme gateway</v>
-      </c>
-      <c r="H4" t="str">
-        <v>File transfer</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>ACT-004</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Ledger</v>
-      </c>
-      <c r="C5" t="str">
-        <v>System</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Posts the provisional credit and any later reversal.</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Applies postings; guarantees a single posting per instruction</v>
-      </c>
-      <c r="F5" t="str">
-        <v>Write postings</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Core banking</v>
-      </c>
-      <c r="H5" t="str">
-        <v>API</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H5"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
-  <cols>
-    <col min="1" max="1" width="26.83203125" customWidth="1"/>
-    <col min="2" max="2" width="26.83203125" customWidth="1"/>
-    <col min="3" max="3" width="26.83203125" customWidth="1"/>
-    <col min="4" max="4" width="26.83203125" customWidth="1"/>
-    <col min="5" max="5" width="26.83203125" customWidth="1"/>
-    <col min="6" max="6" width="26.83203125" customWidth="1"/>
-    <col min="7" max="7" width="26.83203125" customWidth="1"/>
-    <col min="8" max="8" width="26.83203125" customWidth="1"/>
-    <col min="9" max="9" width="26.83203125" customWidth="1"/>
-    <col min="10" max="10" width="26.83203125" customWidth="1"/>
-    <col min="11" max="11" width="26.83203125" customWidth="1"/>
-    <col min="12" max="12" width="26.83203125" customWidth="1"/>
-    <col min="13" max="13" width="26.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Flow</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Flow Name</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Flow Description</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Trigger</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Outcome</v>
-      </c>
-      <c r="F1" t="str">
-        <v>SLA</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Step ID</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Step Name</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Type</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Lane</v>
-      </c>
-      <c r="K1" t="str">
-        <v>Description</v>
-      </c>
-      <c r="L1" t="str">
-        <v>Rules</v>
-      </c>
-      <c r="M1" t="str">
-        <v>Next</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>PF-001</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Raise and settle a card dispute</v>
-      </c>
-      <c r="C2" t="str">
-        <v>From the cardholder tapping Dispute to the case being closed.</v>
-      </c>
-      <c r="D2" t="str">
-        <v>The cardholder disputes a settled transaction</v>
-      </c>
-      <c r="E2" t="str">
-        <v>The case is Resolved or Rejected and the ledger agrees</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Provisional credit within 1 working day; outcome within 45 days</v>
-      </c>
-      <c r="G2" t="str">
-        <v>S1</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Select the transaction</v>
-      </c>
-      <c r="I2" t="str">
-        <v>start</v>
-      </c>
-      <c r="J2" t="str">
-        <v>Cardholder</v>
-      </c>
-      <c r="K2" t="str">
-        <v>The cardholder opens a settled transaction in the app.</v>
-      </c>
-      <c r="L2" t="str">
-        <v/>
-      </c>
-      <c r="M2" t="str">
-        <v>S2</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>PF-001</v>
-      </c>
-      <c r="G3" t="str">
-        <v>S2</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Check the dispute is allowed</v>
-      </c>
-      <c r="I3" t="str">
-        <v>decision</v>
-      </c>
-      <c r="J3" t="str">
-        <v>Disputes service</v>
-      </c>
-      <c r="K3" t="str">
-        <v>Status and the 120-day window are tested.</v>
-      </c>
-      <c r="L3" t="str">
-        <v>RULE-001, RULE-002</v>
-      </c>
-      <c r="M3" t="str">
-        <v>S3, S9</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>PF-001</v>
-      </c>
-      <c r="G4" t="str">
-        <v>S3</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Capture the reason code</v>
-      </c>
-      <c r="I4" t="str">
-        <v>task</v>
-      </c>
-      <c r="J4" t="str">
-        <v>Cardholder</v>
-      </c>
-      <c r="K4" t="str">
-        <v>The cardholder picks a reason and confirms the amount.</v>
-      </c>
-      <c r="L4" t="str">
-        <v/>
-      </c>
-      <c r="M4" t="str">
-        <v>S4</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>PF-001</v>
-      </c>
-      <c r="G5" t="str">
-        <v>S4</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Create the dispute</v>
-      </c>
-      <c r="I5" t="str">
-        <v>system</v>
-      </c>
-      <c r="J5" t="str">
-        <v>Disputes service</v>
-      </c>
-      <c r="K5" t="str">
-        <v>The case is created with the status Submitted.</v>
-      </c>
-      <c r="L5" t="str">
-        <v/>
-      </c>
-      <c r="M5" t="str">
-        <v>S5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>PF-001</v>
-      </c>
-      <c r="G6" t="str">
-        <v>S5</v>
-      </c>
-      <c r="H6" t="str">
-        <v>Post the provisional credit</v>
-      </c>
-      <c r="I6" t="str">
-        <v>system</v>
-      </c>
-      <c r="J6" t="str">
-        <v>Ledger</v>
-      </c>
-      <c r="K6" t="str">
-        <v>The disputed amount is credited while the case is investigated.</v>
-      </c>
-      <c r="L6" t="str">
-        <v>RULE-003</v>
-      </c>
-      <c r="M6" t="str">
-        <v>S6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>PF-001</v>
-      </c>
-      <c r="G7" t="str">
-        <v>S6</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Investigate the case</v>
-      </c>
-      <c r="I7" t="str">
-        <v>task</v>
-      </c>
-      <c r="J7" t="str">
-        <v>Disputes agent</v>
-      </c>
-      <c r="K7" t="str">
-        <v>Evidence is read and the scheme rules applied.</v>
-      </c>
-      <c r="L7" t="str">
-        <v>RULE-004</v>
-      </c>
-      <c r="M7" t="str">
-        <v>S7</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>PF-001</v>
-      </c>
-      <c r="G8" t="str">
-        <v>S7</v>
-      </c>
-      <c r="H8" t="str">
-        <v>Raise the chargeback</v>
-      </c>
-      <c r="I8" t="str">
-        <v>task</v>
-      </c>
-      <c r="J8" t="str">
-        <v>Card scheme</v>
-      </c>
-      <c r="K8" t="str">
-        <v>The chargeback is sent to the scheme for arbitration.</v>
-      </c>
-      <c r="L8" t="str">
-        <v/>
-      </c>
-      <c r="M8" t="str">
-        <v>S8</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>PF-001</v>
-      </c>
-      <c r="G9" t="str">
-        <v>S8</v>
-      </c>
-      <c r="H9" t="str">
-        <v>Close the case</v>
-      </c>
-      <c r="I9" t="str">
-        <v>end</v>
-      </c>
-      <c r="J9" t="str">
-        <v>Disputes service</v>
-      </c>
-      <c r="K9" t="str">
-        <v>The case is Resolved; the provisional credit stands or is reversed.</v>
-      </c>
-      <c r="L9" t="str">
-        <v/>
-      </c>
-      <c r="M9" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>PF-001</v>
-      </c>
-      <c r="G10" t="str">
-        <v>S9</v>
-      </c>
-      <c r="H10" t="str">
-        <v>Refuse the dispute</v>
-      </c>
-      <c r="I10" t="str">
-        <v>end</v>
-      </c>
-      <c r="J10" t="str">
-        <v>Disputes service</v>
-      </c>
-      <c r="K10" t="str">
-        <v>The cardholder is told which condition failed.</v>
-      </c>
-      <c r="L10" t="str">
-        <v/>
-      </c>
-      <c r="M10" t="str">
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M10"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I6"/>
   <cols>
@@ -2215,7 +1092,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K4"/>
   <cols>
@@ -2379,7 +1256,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K5"/>
   <cols>
@@ -2578,7 +1455,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L4"/>
   <cols>
@@ -2768,4 +1645,1892 @@
     <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <cols>
+    <col min="1" max="1" width="26.83203125" customWidth="1"/>
+    <col min="2" max="2" width="26.83203125" customWidth="1"/>
+    <col min="3" max="3" width="26.83203125" customWidth="1"/>
+    <col min="4" max="4" width="26.83203125" customWidth="1"/>
+    <col min="5" max="5" width="26.83203125" customWidth="1"/>
+    <col min="6" max="6" width="26.83203125" customWidth="1"/>
+    <col min="7" max="7" width="26.83203125" customWidth="1"/>
+    <col min="8" max="8" width="26.83203125" customWidth="1"/>
+    <col min="9" max="9" width="26.83203125" customWidth="1"/>
+    <col min="10" max="10" width="26.83203125" customWidth="1"/>
+    <col min="11" max="11" width="26.83203125" customWidth="1"/>
+    <col min="12" max="12" width="26.83203125" customWidth="1"/>
+    <col min="13" max="13" width="26.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Scenario</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Suite</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Preconditions</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Steps</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Expected Result</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Status</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Priority</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Type</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Requirement</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Last Run</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Executed By</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Defect</v>
+      </c>
+    </row>
+    <row r="2" xml:space="preserve">
+      <c r="A2" t="str">
+        <v>TC-001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>A settled transaction inside the window can be disputed</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Disputes</v>
+      </c>
+      <c r="D2" t="str">
+        <v>A card with a settled transaction dated 30 days ago</v>
+      </c>
+      <c r="E2" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Open the transaction -&gt; the Dispute action is available
+2. Choose a reason and confirm -&gt; a reference is shown</v>
+      </c>
+      <c r="F2" t="str">
+        <v>The dispute exists with the status Submitted.</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Functional</v>
+      </c>
+      <c r="J2" t="str">
+        <v>BR-001</v>
+      </c>
+      <c r="K2" t="str">
+        <v>2026-02-19</v>
+      </c>
+      <c r="L2" t="str">
+        <v>Saadaoui Abdessalem</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>TC-002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>A transaction older than 120 days cannot be disputed</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Disputes</v>
+      </c>
+      <c r="D3" t="str">
+        <v>A card with a settled transaction dated 130 days ago</v>
+      </c>
+      <c r="E3" t="str">
+        <v>1. Open the transaction -&gt; the Dispute action is disabled and the reason is shown</v>
+      </c>
+      <c r="F3" t="str">
+        <v>No dispute is created and the cardholder is told why.</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="J3" t="str">
+        <v>BR-001</v>
+      </c>
+      <c r="K3" t="str">
+        <v>2026-02-19</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Saadaoui Abdessalem</v>
+      </c>
+    </row>
+    <row r="4" xml:space="preserve">
+      <c r="A4" t="str">
+        <v>TC-003</v>
+      </c>
+      <c r="B4" t="str">
+        <v>A provisional credit is posted for the disputed amount</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Settlement</v>
+      </c>
+      <c r="D4" t="str">
+        <v>A dispute of 84.50 accepted before the end-of-day run</v>
+      </c>
+      <c r="E4" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Run end of day -&gt; a posting appears
+2. Read the posting -&gt; the amount is 84.50</v>
+      </c>
+      <c r="F4" t="str">
+        <v>One provisional credit of 84.50 and no second posting.</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Integration</v>
+      </c>
+      <c r="J4" t="str">
+        <v>BR-002</v>
+      </c>
+      <c r="K4" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="L4" t="str">
+        <v>Saadaoui Abdessalem</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>TC-004</v>
+      </c>
+      <c r="B5" t="str">
+        <v>The sixth evidence file is refused</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Evidence</v>
+      </c>
+      <c r="D5" t="str">
+        <v>A dispute Under Review with five files attached</v>
+      </c>
+      <c r="E5" t="str">
+        <v>1. Attach a sixth file -&gt; the error ATTACHMENT_LIMIT is shown</v>
+      </c>
+      <c r="F5" t="str">
+        <v>The file is refused and the five existing files are untouched.</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Failed</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I5" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="J5" t="str">
+        <v>BR-003</v>
+      </c>
+      <c r="K5" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="L5" t="str">
+        <v>Saadaoui Abdessalem</v>
+      </c>
+      <c r="M5" t="str">
+        <v>DEF-118</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>TC-005</v>
+      </c>
+      <c r="B6" t="str">
+        <v>One notification per status change</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Notifications</v>
+      </c>
+      <c r="D6" t="str">
+        <v>A dispute with the status Submitted</v>
+      </c>
+      <c r="E6" t="str">
+        <v>1. Move it to Under Review -&gt; one notification is sent</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Exactly one notification, not one per retry.</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I6" t="str">
+        <v>Functional</v>
+      </c>
+      <c r="J6" t="str">
+        <v>BR-004</v>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:M6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L4"/>
+  <cols>
+    <col min="1" max="1" width="26.83203125" customWidth="1"/>
+    <col min="2" max="2" width="26.83203125" customWidth="1"/>
+    <col min="3" max="3" width="26.83203125" customWidth="1"/>
+    <col min="4" max="4" width="26.83203125" customWidth="1"/>
+    <col min="5" max="5" width="26.83203125" customWidth="1"/>
+    <col min="6" max="6" width="26.83203125" customWidth="1"/>
+    <col min="7" max="7" width="26.83203125" customWidth="1"/>
+    <col min="8" max="8" width="26.83203125" customWidth="1"/>
+    <col min="9" max="9" width="26.83203125" customWidth="1"/>
+    <col min="10" max="10" width="26.83203125" customWidth="1"/>
+    <col min="11" max="11" width="26.83203125" customWidth="1"/>
+    <col min="12" max="12" width="26.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Format</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Description</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Category</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Version</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Author</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Last Updated</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Size</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Status</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Confidentiality</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Requirements</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>DOC-001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Card disputes — business requirements</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Word</v>
+      </c>
+      <c r="D2" t="str">
+        <v>The signed requirements pack behind BR-001 and BR-002.</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Requirements</v>
+      </c>
+      <c r="F2" t="str">
+        <v>1.2</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Saadaoui Abdessalem</v>
+      </c>
+      <c r="H2" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="I2" t="str">
+        <v>412 KB</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Approved</v>
+      </c>
+      <c r="K2" t="str">
+        <v>Internal</v>
+      </c>
+      <c r="L2" t="str">
+        <v>BR-001, BR-002</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>DOC-002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Disputes API contract</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Swagger</v>
+      </c>
+      <c r="D3" t="str">
+        <v>OpenAPI 3.1 definition of the four dispute endpoints.</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Interface</v>
+      </c>
+      <c r="F3" t="str">
+        <v>1.0.0</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Saadaoui Abdessalem</v>
+      </c>
+      <c r="H3" t="str">
+        <v>2026-02-15</v>
+      </c>
+      <c r="I3" t="str">
+        <v>38 KB</v>
+      </c>
+      <c r="J3" t="str">
+        <v>In Review</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Internal</v>
+      </c>
+      <c r="L3" t="str">
+        <v>BR-001, BR-003</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>DOC-003</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Dispute process model</v>
+      </c>
+      <c r="C4" t="str">
+        <v>BPMN</v>
+      </c>
+      <c r="D4" t="str">
+        <v>The BPMN 2.0 file behind the process flow.</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Process</v>
+      </c>
+      <c r="F4" t="str">
+        <v>1.0</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Saadaoui Abdessalem</v>
+      </c>
+      <c r="H4" t="str">
+        <v>2026-02-14</v>
+      </c>
+      <c r="I4" t="str">
+        <v>24 KB</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Approved</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Internal</v>
+      </c>
+      <c r="L4" t="str">
+        <v>BR-001</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E8"/>
+  <cols>
+    <col min="1" max="1" width="26.83203125" customWidth="1"/>
+    <col min="2" max="2" width="26.83203125" customWidth="1"/>
+    <col min="3" max="3" width="26.83203125" customWidth="1"/>
+    <col min="4" max="4" width="26.83203125" customWidth="1"/>
+    <col min="5" max="5" width="26.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Requirement</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Given</v>
+      </c>
+      <c r="D1" t="str">
+        <v>When</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Then</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>AC-001.1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>BR-001</v>
+      </c>
+      <c r="C2" t="str">
+        <v>a settled card transaction dated within the last 120 days</v>
+      </c>
+      <c r="D2" t="str">
+        <v>the cardholder raises a dispute and selects a reason code</v>
+      </c>
+      <c r="E2" t="str">
+        <v>the dispute is created with the status Submitted and a reference is shown</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>AC-001.2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>BR-001</v>
+      </c>
+      <c r="C3" t="str">
+        <v>a transaction older than 120 days</v>
+      </c>
+      <c r="D3" t="str">
+        <v>the cardholder opens it</v>
+      </c>
+      <c r="E3" t="str">
+        <v>the dispute action is unavailable and the reason is stated on screen</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>AC-001.3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>BR-001</v>
+      </c>
+      <c r="C4" t="str">
+        <v>a transaction that already has an open dispute</v>
+      </c>
+      <c r="D4" t="str">
+        <v>the cardholder tries to dispute it again</v>
+      </c>
+      <c r="E4" t="str">
+        <v>the existing case is shown instead of a second one being created</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>AC-002.1</v>
+      </c>
+      <c r="B5" t="str">
+        <v>BR-002</v>
+      </c>
+      <c r="C5" t="str">
+        <v>a dispute accepted at 16:00 on a working day</v>
+      </c>
+      <c r="D5" t="str">
+        <v>the next end-of-day run completes</v>
+      </c>
+      <c r="E5" t="str">
+        <v>a provisional credit for the full disputed amount is posted</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>AC-002.2</v>
+      </c>
+      <c r="B6" t="str">
+        <v>BR-002</v>
+      </c>
+      <c r="C6" t="str">
+        <v>a dispute later rejected</v>
+      </c>
+      <c r="D6" t="str">
+        <v>the rejection is recorded</v>
+      </c>
+      <c r="E6" t="str">
+        <v>the provisional credit is reversed and the cardholder is told why</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>AC-003.1</v>
+      </c>
+      <c r="B7" t="str">
+        <v>BR-003</v>
+      </c>
+      <c r="C7" t="str">
+        <v>a dispute with the status Under Review and four files already attached</v>
+      </c>
+      <c r="D7" t="str">
+        <v>the cardholder attaches a fifth file of 8 MB</v>
+      </c>
+      <c r="E7" t="str">
+        <v>the file is accepted and the attach action is then disabled</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>AC-004.1</v>
+      </c>
+      <c r="B8" t="str">
+        <v>BR-004</v>
+      </c>
+      <c r="C8" t="str">
+        <v>a dispute that moves from Submitted to Under Review</v>
+      </c>
+      <c r="D8" t="str">
+        <v>the status change is saved</v>
+      </c>
+      <c r="E8" t="str">
+        <v>exactly one notification is sent to the cardholder</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E8"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J5"/>
+  <cols>
+    <col min="1" max="1" width="26.83203125" customWidth="1"/>
+    <col min="2" max="2" width="26.83203125" customWidth="1"/>
+    <col min="3" max="3" width="26.83203125" customWidth="1"/>
+    <col min="4" max="4" width="26.83203125" customWidth="1"/>
+    <col min="5" max="5" width="26.83203125" customWidth="1"/>
+    <col min="6" max="6" width="26.83203125" customWidth="1"/>
+    <col min="7" max="7" width="26.83203125" customWidth="1"/>
+    <col min="8" max="8" width="26.83203125" customWidth="1"/>
+    <col min="9" max="9" width="26.83203125" customWidth="1"/>
+    <col min="10" max="10" width="26.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Description</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Logic</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Priority</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Source</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Status</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Category</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Owner</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Effective From</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Requirements</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>RULE-001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>A dispute may only be raised against a settled transaction.</v>
+      </c>
+      <c r="C2" t="str">
+        <v>IF transaction.status &lt;&gt; 'SETTLED' THEN reject WITH 'NOT_DISPUTABLE'</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Scheme rules, chapter 11</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Approved</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Eligibility</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Saadaoui Abdessalem</v>
+      </c>
+      <c r="I2" t="str">
+        <v>2026-01-01</v>
+      </c>
+      <c r="J2" t="str">
+        <v>BR-001</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>RULE-002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>A transaction is disputable for 120 days after its settlement date.</v>
+      </c>
+      <c r="C3" t="str">
+        <v>IF today - transaction.settled_date &gt; 120 THEN reject WITH 'WINDOW_CLOSED'</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Scheme rules, chapter 11</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Approved</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Eligibility</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Saadaoui Abdessalem</v>
+      </c>
+      <c r="I3" t="str">
+        <v>2026-01-01</v>
+      </c>
+      <c r="J3" t="str">
+        <v>BR-001</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>RULE-003</v>
+      </c>
+      <c r="B4" t="str">
+        <v>A provisional credit equals the disputed amount, never more.</v>
+      </c>
+      <c r="C4" t="str">
+        <v>credit.amount = dispute.amount AND credit.amount &lt;= transaction.amount</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Treasury policy 7.1</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Approved</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Settlement</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Saadaoui Abdessalem</v>
+      </c>
+      <c r="I4" t="str">
+        <v>2026-01-01</v>
+      </c>
+      <c r="J4" t="str">
+        <v>BR-002</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>RULE-004</v>
+      </c>
+      <c r="B5" t="str">
+        <v>At most five evidence files, each at most 10 MB, per dispute.</v>
+      </c>
+      <c r="C5" t="str">
+        <v>IF files.count &gt; 5 OR file.size &gt; 10485760 THEN reject WITH 'ATTACHMENT_LIMIT'</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Operations handbook 3.4</v>
+      </c>
+      <c r="F5" t="str">
+        <v>In Review</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Evidence</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Saadaoui Abdessalem</v>
+      </c>
+      <c r="I5" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="J5" t="str">
+        <v>BR-003</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:J5"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H5"/>
+  <cols>
+    <col min="1" max="1" width="26.83203125" customWidth="1"/>
+    <col min="2" max="2" width="26.83203125" customWidth="1"/>
+    <col min="3" max="3" width="26.83203125" customWidth="1"/>
+    <col min="4" max="4" width="26.83203125" customWidth="1"/>
+    <col min="5" max="5" width="26.83203125" customWidth="1"/>
+    <col min="6" max="6" width="26.83203125" customWidth="1"/>
+    <col min="7" max="7" width="26.83203125" customWidth="1"/>
+    <col min="8" max="8" width="26.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Type</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Description</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Responsibilities</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Permissions</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Systems</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Channel</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>ACT-001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Cardholder</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Human</v>
+      </c>
+      <c r="D2" t="str">
+        <v>The retail customer whose card was charged.</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Raises the dispute; supplies evidence; accepts the outcome</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Read own transactions; create dispute; attach evidence</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Mobile app; internet banking</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Mobile</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>ACT-002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Disputes agent</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Human</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Back-office analyst who investigates the case against the scheme rules.</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Reviews evidence; decides the outcome; raises the chargeback</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Read all disputes; change status; post adjustments</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Disputes console; card management system</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Back Office</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>ACT-003</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Card scheme</v>
+      </c>
+      <c r="C4" t="str">
+        <v>External</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Visa or Mastercard, which arbitrates the chargeback.</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Accepts the chargeback; rules on representment</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Receive chargeback messages</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Scheme gateway</v>
+      </c>
+      <c r="H4" t="str">
+        <v>File transfer</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>ACT-004</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Ledger</v>
+      </c>
+      <c r="C5" t="str">
+        <v>System</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Posts the provisional credit and any later reversal.</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Applies postings; guarantees a single posting per instruction</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Write postings</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Core banking</v>
+      </c>
+      <c r="H5" t="str">
+        <v>API</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H5"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M10"/>
+  <cols>
+    <col min="1" max="1" width="26.83203125" customWidth="1"/>
+    <col min="2" max="2" width="26.83203125" customWidth="1"/>
+    <col min="3" max="3" width="26.83203125" customWidth="1"/>
+    <col min="4" max="4" width="26.83203125" customWidth="1"/>
+    <col min="5" max="5" width="26.83203125" customWidth="1"/>
+    <col min="6" max="6" width="26.83203125" customWidth="1"/>
+    <col min="7" max="7" width="26.83203125" customWidth="1"/>
+    <col min="8" max="8" width="26.83203125" customWidth="1"/>
+    <col min="9" max="9" width="26.83203125" customWidth="1"/>
+    <col min="10" max="10" width="26.83203125" customWidth="1"/>
+    <col min="11" max="11" width="26.83203125" customWidth="1"/>
+    <col min="12" max="12" width="26.83203125" customWidth="1"/>
+    <col min="13" max="13" width="26.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Flow</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Flow Name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Flow Description</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Trigger</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Outcome</v>
+      </c>
+      <c r="F1" t="str">
+        <v>SLA</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Step ID</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Step Name</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Type</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Lane</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Description</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Rules</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Next</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>PF-001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Raise and settle a card dispute</v>
+      </c>
+      <c r="C2" t="str">
+        <v>From the cardholder tapping Dispute to the case being closed.</v>
+      </c>
+      <c r="D2" t="str">
+        <v>The cardholder disputes a settled transaction</v>
+      </c>
+      <c r="E2" t="str">
+        <v>The case is Resolved or Rejected and the ledger agrees</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Provisional credit within 1 working day; outcome within 45 days</v>
+      </c>
+      <c r="G2" t="str">
+        <v>S1</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Select the transaction</v>
+      </c>
+      <c r="I2" t="str">
+        <v>start</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Cardholder</v>
+      </c>
+      <c r="K2" t="str">
+        <v>The cardholder opens a settled transaction in the app.</v>
+      </c>
+      <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2" t="str">
+        <v>S2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>PF-001</v>
+      </c>
+      <c r="G3" t="str">
+        <v>S2</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Check the dispute is allowed</v>
+      </c>
+      <c r="I3" t="str">
+        <v>decision</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Disputes service</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Status and the 120-day window are tested.</v>
+      </c>
+      <c r="L3" t="str">
+        <v>RULE-001, RULE-002</v>
+      </c>
+      <c r="M3" t="str">
+        <v>S3, S9</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>PF-001</v>
+      </c>
+      <c r="G4" t="str">
+        <v>S3</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Capture the reason code</v>
+      </c>
+      <c r="I4" t="str">
+        <v>task</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Cardholder</v>
+      </c>
+      <c r="K4" t="str">
+        <v>The cardholder picks a reason and confirms the amount.</v>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
+        <v>S4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>PF-001</v>
+      </c>
+      <c r="G5" t="str">
+        <v>S4</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Create the dispute</v>
+      </c>
+      <c r="I5" t="str">
+        <v>system</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Disputes service</v>
+      </c>
+      <c r="K5" t="str">
+        <v>The case is created with the status Submitted.</v>
+      </c>
+      <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
+        <v>S5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>PF-001</v>
+      </c>
+      <c r="G6" t="str">
+        <v>S5</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Post the provisional credit</v>
+      </c>
+      <c r="I6" t="str">
+        <v>system</v>
+      </c>
+      <c r="J6" t="str">
+        <v>Ledger</v>
+      </c>
+      <c r="K6" t="str">
+        <v>The disputed amount is credited while the case is investigated.</v>
+      </c>
+      <c r="L6" t="str">
+        <v>RULE-003</v>
+      </c>
+      <c r="M6" t="str">
+        <v>S6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>PF-001</v>
+      </c>
+      <c r="G7" t="str">
+        <v>S6</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Investigate the case</v>
+      </c>
+      <c r="I7" t="str">
+        <v>task</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Disputes agent</v>
+      </c>
+      <c r="K7" t="str">
+        <v>Evidence is read and the scheme rules applied.</v>
+      </c>
+      <c r="L7" t="str">
+        <v>RULE-004</v>
+      </c>
+      <c r="M7" t="str">
+        <v>S7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>PF-001</v>
+      </c>
+      <c r="G8" t="str">
+        <v>S7</v>
+      </c>
+      <c r="H8" t="str">
+        <v>Raise the chargeback</v>
+      </c>
+      <c r="I8" t="str">
+        <v>task</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Card scheme</v>
+      </c>
+      <c r="K8" t="str">
+        <v>The chargeback is sent to the scheme for arbitration.</v>
+      </c>
+      <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8" t="str">
+        <v>S8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>PF-001</v>
+      </c>
+      <c r="G9" t="str">
+        <v>S8</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Close the case</v>
+      </c>
+      <c r="I9" t="str">
+        <v>end</v>
+      </c>
+      <c r="J9" t="str">
+        <v>Disputes service</v>
+      </c>
+      <c r="K9" t="str">
+        <v>The case is Resolved; the provisional credit stands or is reversed.</v>
+      </c>
+      <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>PF-001</v>
+      </c>
+      <c r="G10" t="str">
+        <v>S9</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Refuse the dispute</v>
+      </c>
+      <c r="I10" t="str">
+        <v>end</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Disputes service</v>
+      </c>
+      <c r="K10" t="str">
+        <v>The cardholder is told which condition failed.</v>
+      </c>
+      <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:M10"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E4"/>
+  <cols>
+    <col min="1" max="1" width="26.83203125" customWidth="1"/>
+    <col min="2" max="2" width="26.83203125" customWidth="1"/>
+    <col min="3" max="3" width="26.83203125" customWidth="1"/>
+    <col min="4" max="4" width="26.83203125" customWidth="1"/>
+    <col min="5" max="5" width="26.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Title</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Summary</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Requirements</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Business Logic</v>
+      </c>
+    </row>
+    <row r="2" xml:space="preserve">
+      <c r="A2" t="str">
+        <v>FS-001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Raising a dispute</v>
+      </c>
+      <c r="C2" t="str">
+        <v>How a dispute is created from a settled transaction: what is checked, what is stored, and what the cardholder is told at each refusal.</v>
+      </c>
+      <c r="D2" t="str">
+        <v>BR-001</v>
+      </c>
+      <c r="E2" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Read the transaction and confirm it is settled
+2. Confirm the settlement date is within 120 days of today
+3. Confirm no open dispute already exists for it
+4. Store the dispute with the status Submitted and return its reference</v>
+      </c>
+    </row>
+    <row r="3" xml:space="preserve">
+      <c r="A3" t="str">
+        <v>FS-002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Provisional credit</v>
+      </c>
+      <c r="C3" t="str">
+        <v>How the disputed amount is returned to the cardholder while the case is investigated, and how it is reversed if the dispute fails.</v>
+      </c>
+      <c r="D3" t="str">
+        <v>BR-002</v>
+      </c>
+      <c r="E3" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. On acceptance, queue a posting for the disputed amount
+2. Post it in the next end-of-day run
+3. On rejection, reverse the posting and notify the cardholder</v>
+      </c>
+    </row>
+    <row r="4" xml:space="preserve">
+      <c r="A4" t="str">
+        <v>FS-003</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Evidence handling</v>
+      </c>
+      <c r="C4" t="str">
+        <v>What a cardholder may attach to an open case, and what is refused.</v>
+      </c>
+      <c r="D4" t="str">
+        <v>BR-003</v>
+      </c>
+      <c r="E4" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Accept files only while the case is Under Review
+2. Refuse a sixth file, or any file over 10 MB
+3. Store the file against the dispute, never against the transaction</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E4"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G9"/>
+  <cols>
+    <col min="1" max="1" width="26.83203125" customWidth="1"/>
+    <col min="2" max="2" width="26.83203125" customWidth="1"/>
+    <col min="3" max="3" width="26.83203125" customWidth="1"/>
+    <col min="4" max="4" width="26.83203125" customWidth="1"/>
+    <col min="5" max="5" width="26.83203125" customWidth="1"/>
+    <col min="6" max="6" width="26.83203125" customWidth="1"/>
+    <col min="7" max="7" width="26.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Section</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Type</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Length</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Mandatory</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Description</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Example</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>FS-001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>transactionId</v>
+      </c>
+      <c r="C2" t="str">
+        <v>uuid</v>
+      </c>
+      <c r="D2" t="str">
+        <v>36</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="F2" t="str">
+        <v>The settled transaction being disputed.</v>
+      </c>
+      <c r="G2" t="str">
+        <v>9f2c1b7e-4a2d-4f9a-8b31-0c5e2a7d9f10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>FS-001</v>
+      </c>
+      <c r="B3" t="str">
+        <v>reasonCode</v>
+      </c>
+      <c r="C3" t="str">
+        <v>varchar</v>
+      </c>
+      <c r="D3" t="str">
+        <v>10</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Why the cardholder disputes the charge, in scheme terms.</v>
+      </c>
+      <c r="G3" t="str">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>FS-001</v>
+      </c>
+      <c r="B4" t="str">
+        <v>amount</v>
+      </c>
+      <c r="C4" t="str">
+        <v>numeric</v>
+      </c>
+      <c r="D4" t="str">
+        <v>15,2</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="F4" t="str">
+        <v>The disputed amount; may be less than the transaction, never more.</v>
+      </c>
+      <c r="G4" t="str">
+        <v>84.50</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>FS-001</v>
+      </c>
+      <c r="B5" t="str">
+        <v>description</v>
+      </c>
+      <c r="C5" t="str">
+        <v>varchar</v>
+      </c>
+      <c r="D5" t="str">
+        <v>500</v>
+      </c>
+      <c r="E5" t="str">
+        <v>No</v>
+      </c>
+      <c r="F5" t="str">
+        <v>The cardholder's own account of what happened.</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Charged twice for one meal</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>FS-002</v>
+      </c>
+      <c r="B6" t="str">
+        <v>postingId</v>
+      </c>
+      <c r="C6" t="str">
+        <v>uuid</v>
+      </c>
+      <c r="D6" t="str">
+        <v>36</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="F6" t="str">
+        <v>The ledger posting that carries the provisional credit.</v>
+      </c>
+      <c r="G6" t="str">
+        <v>3d81c0aa-71f4-4d2e-9c6b-6f0b2b1e77a2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>FS-002</v>
+      </c>
+      <c r="B7" t="str">
+        <v>valueDate</v>
+      </c>
+      <c r="C7" t="str">
+        <v>date</v>
+      </c>
+      <c r="D7" t="str">
+        <v>10</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="F7" t="str">
+        <v>The date the credit takes effect on the account.</v>
+      </c>
+      <c r="G7" t="str">
+        <v>2026-02-11</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>FS-003</v>
+      </c>
+      <c r="B8" t="str">
+        <v>fileName</v>
+      </c>
+      <c r="C8" t="str">
+        <v>varchar</v>
+      </c>
+      <c r="D8" t="str">
+        <v>255</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="F8" t="str">
+        <v>The name of the attached evidence file.</v>
+      </c>
+      <c r="G8" t="str">
+        <v>receipt-2026-02-08.pdf</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>FS-003</v>
+      </c>
+      <c r="B9" t="str">
+        <v>sizeBytes</v>
+      </c>
+      <c r="C9" t="str">
+        <v>bigint</v>
+      </c>
+      <c r="D9" t="str">
+        <v>—</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="F9" t="str">
+        <v>File size, checked against the 10 MB limit.</v>
+      </c>
+      <c r="G9" t="str">
+        <v>2411008</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G9"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E9"/>
+  <cols>
+    <col min="1" max="1" width="26.83203125" customWidth="1"/>
+    <col min="2" max="2" width="26.83203125" customWidth="1"/>
+    <col min="3" max="3" width="26.83203125" customWidth="1"/>
+    <col min="4" max="4" width="26.83203125" customWidth="1"/>
+    <col min="5" max="5" width="26.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Section</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Field</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Rule</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Error Code</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Severity</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>FS-001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>transactionId</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Must reference a transaction whose status is SETTLED</v>
+      </c>
+      <c r="D2" t="str">
+        <v>NOT_DISPUTABLE</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Blocking</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>FS-001</v>
+      </c>
+      <c r="B3" t="str">
+        <v>transactionId</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Settlement date must be within 120 days of today</v>
+      </c>
+      <c r="D3" t="str">
+        <v>WINDOW_CLOSED</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Blocking</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>FS-001</v>
+      </c>
+      <c r="B4" t="str">
+        <v>transactionId</v>
+      </c>
+      <c r="C4" t="str">
+        <v>No dispute may already be open against this transaction</v>
+      </c>
+      <c r="D4" t="str">
+        <v>ALREADY_DISPUTED</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Blocking</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>FS-001</v>
+      </c>
+      <c r="B5" t="str">
+        <v>amount</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Must be greater than zero and at most the transaction amount</v>
+      </c>
+      <c r="D5" t="str">
+        <v>AMOUNT_INVALID</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Blocking</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>FS-001</v>
+      </c>
+      <c r="B6" t="str">
+        <v>reasonCode</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Must be one of the scheme reason codes in force</v>
+      </c>
+      <c r="D6" t="str">
+        <v>REASON_UNKNOWN</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Blocking</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>FS-002</v>
+      </c>
+      <c r="B7" t="str">
+        <v>amount</v>
+      </c>
+      <c r="C7" t="str">
+        <v>The credit must equal the disputed amount exactly</v>
+      </c>
+      <c r="D7" t="str">
+        <v>CREDIT_MISMATCH</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Blocking</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>FS-003</v>
+      </c>
+      <c r="B8" t="str">
+        <v>sizeBytes</v>
+      </c>
+      <c r="C8" t="str">
+        <v>At most 10485760 bytes per file</v>
+      </c>
+      <c r="D8" t="str">
+        <v>ATTACHMENT_TOO_LARGE</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Blocking</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>FS-003</v>
+      </c>
+      <c r="B9" t="str">
+        <v>fileName</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Extension should be pdf, png or jpg</v>
+      </c>
+      <c r="D9" t="str">
+        <v>ATTACHMENT_TYPE</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Warning</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E9"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E8"/>
+  <cols>
+    <col min="1" max="1" width="26.83203125" customWidth="1"/>
+    <col min="2" max="2" width="26.83203125" customWidth="1"/>
+    <col min="3" max="3" width="26.83203125" customWidth="1"/>
+    <col min="4" max="4" width="26.83203125" customWidth="1"/>
+    <col min="5" max="5" width="26.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Section</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Code</v>
+      </c>
+      <c r="C1" t="str">
+        <v>HTTP Status</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Message</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Handling</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>FS-001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>NOT_DISPUTABLE</v>
+      </c>
+      <c r="C2">
+        <v>422</v>
+      </c>
+      <c r="D2" t="str">
+        <v>This transaction cannot be disputed yet.</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Tell the cardholder to wait until the payment settles, and show the date.</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>FS-001</v>
+      </c>
+      <c r="B3" t="str">
+        <v>WINDOW_CLOSED</v>
+      </c>
+      <c r="C3">
+        <v>422</v>
+      </c>
+      <c r="D3" t="str">
+        <v>The 120-day window for disputing this payment has passed.</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Show the deadline that passed and offer the contact centre.</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>FS-001</v>
+      </c>
+      <c r="B4" t="str">
+        <v>ALREADY_DISPUTED</v>
+      </c>
+      <c r="C4">
+        <v>409</v>
+      </c>
+      <c r="D4" t="str">
+        <v>There is already an open dispute for this payment.</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Take the cardholder to the existing case rather than refusing.</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>FS-001</v>
+      </c>
+      <c r="B5" t="str">
+        <v>AMOUNT_INVALID</v>
+      </c>
+      <c r="C5">
+        <v>400</v>
+      </c>
+      <c r="D5" t="str">
+        <v>The disputed amount is not valid.</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Reset the field to the full transaction amount.</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>FS-002</v>
+      </c>
+      <c r="B6" t="str">
+        <v>CREDIT_MISMATCH</v>
+      </c>
+      <c r="C6">
+        <v>500</v>
+      </c>
+      <c r="D6" t="str">
+        <v>The provisional credit does not match the disputed amount.</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Hold the posting and raise an operations alert; never post a partial credit.</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>FS-003</v>
+      </c>
+      <c r="B7" t="str">
+        <v>ATTACHMENT_LIMIT</v>
+      </c>
+      <c r="C7">
+        <v>422</v>
+      </c>
+      <c r="D7" t="str">
+        <v>You can attach up to five files.</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Hide the attach action once five files exist, rather than failing on the sixth.</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>FS-003</v>
+      </c>
+      <c r="B8" t="str">
+        <v>ATTACHMENT_TOO_LARGE</v>
+      </c>
+      <c r="C8">
+        <v>413</v>
+      </c>
+      <c r="D8" t="str">
+        <v>That file is larger than 10 MB.</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Say the limit before the upload starts, not after it finishes.</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E8"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/public/fa/example-project.xlsx
+++ b/public/fa/example-project.xlsx
@@ -3,22 +3,28 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Requirements" sheetId="1" r:id="rId1"/>
-    <sheet name="Acceptance Criteria" sheetId="2" r:id="rId2"/>
-    <sheet name="Business Rules" sheetId="3" r:id="rId3"/>
-    <sheet name="Actors" sheetId="4" r:id="rId4"/>
-    <sheet name="Process Steps" sheetId="5" r:id="rId5"/>
-    <sheet name="Spec Sections" sheetId="6" r:id="rId6"/>
-    <sheet name="Spec Fields" sheetId="7" r:id="rId7"/>
-    <sheet name="Spec Validations" sheetId="8" r:id="rId8"/>
-    <sheet name="Spec Errors" sheetId="9" r:id="rId9"/>
-    <sheet name="Spec Edge Cases" sheetId="10" r:id="rId10"/>
-    <sheet name="Diagrams" sheetId="11" r:id="rId11"/>
-    <sheet name="Wireframes" sheetId="12" r:id="rId12"/>
-    <sheet name="API Endpoints" sheetId="13" r:id="rId13"/>
-    <sheet name="SQL Validations" sheetId="14" r:id="rId14"/>
-    <sheet name="Test Cases" sheetId="15" r:id="rId15"/>
-    <sheet name="Documents" sheetId="16" r:id="rId16"/>
+    <sheet name="Project" sheetId="1" r:id="rId1"/>
+    <sheet name="Scope" sheetId="2" r:id="rId2"/>
+    <sheet name="Stakeholders" sheetId="3" r:id="rId3"/>
+    <sheet name="Timeline" sheetId="4" r:id="rId4"/>
+    <sheet name="Dependencies" sheetId="5" r:id="rId5"/>
+    <sheet name="Risks" sheetId="6" r:id="rId6"/>
+    <sheet name="Requirements" sheetId="7" r:id="rId7"/>
+    <sheet name="Acceptance Criteria" sheetId="8" r:id="rId8"/>
+    <sheet name="Business Rules" sheetId="9" r:id="rId9"/>
+    <sheet name="Actors" sheetId="10" r:id="rId10"/>
+    <sheet name="Process Steps" sheetId="11" r:id="rId11"/>
+    <sheet name="Spec Sections" sheetId="12" r:id="rId12"/>
+    <sheet name="Spec Fields" sheetId="13" r:id="rId13"/>
+    <sheet name="Spec Validations" sheetId="14" r:id="rId14"/>
+    <sheet name="Spec Errors" sheetId="15" r:id="rId15"/>
+    <sheet name="Spec Edge Cases" sheetId="16" r:id="rId16"/>
+    <sheet name="Diagrams" sheetId="17" r:id="rId17"/>
+    <sheet name="Wireframes" sheetId="18" r:id="rId18"/>
+    <sheet name="API Endpoints" sheetId="19" r:id="rId19"/>
+    <sheet name="SQL Validations" sheetId="20" r:id="rId20"/>
+    <sheet name="Test Cases" sheetId="21" r:id="rId21"/>
+    <sheet name="Documents" sheetId="22" r:id="rId22"/>
   </sheets>
 </workbook>
 </file>
@@ -412,7 +418,325 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:B19"/>
+  <cols>
+    <col min="1" max="1" width="26.83203125" customWidth="1"/>
+    <col min="2" max="2" width="26.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Value</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Name</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Card Disputes &amp; Chargeback Automation</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Code</v>
+      </c>
+      <c r="B3" t="str">
+        <v>CDA-1.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Domain</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Banking</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Sub Domain</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Cards &amp; Disputes</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Status</v>
+      </c>
+      <c r="B6" t="str">
+        <v>In Progress</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Version</v>
+      </c>
+      <c r="B7" t="str">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Release</v>
+      </c>
+      <c r="B8" t="str">
+        <v>R2026.03</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Owner</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Saadaoui Abdessalem</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Owner Role</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Lead Functional Analyst</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Business Owner</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Head of Card Operations</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Programme</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Cards Modernisation</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Summary</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Automating the card dispute lifecycle from the cardholder raising a case to the chargeback being settled with the scheme.</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Business Objective</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Cut the cost per dispute by 45% and post every provisional credit within one working day.</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Start Date</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-01-05</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Target Date</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Completion</v>
+      </c>
+      <c r="B17" t="str">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Regulatory Drivers</v>
+      </c>
+      <c r="B18" t="str">
+        <v>PSD2 Article 74; Scheme rules chapter 11</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Tags</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Cards, Disputes, Automation</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B19"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H5"/>
+  <cols>
+    <col min="1" max="1" width="26.83203125" customWidth="1"/>
+    <col min="2" max="2" width="26.83203125" customWidth="1"/>
+    <col min="3" max="3" width="26.83203125" customWidth="1"/>
+    <col min="4" max="4" width="26.83203125" customWidth="1"/>
+    <col min="5" max="5" width="26.83203125" customWidth="1"/>
+    <col min="6" max="6" width="26.83203125" customWidth="1"/>
+    <col min="7" max="7" width="26.83203125" customWidth="1"/>
+    <col min="8" max="8" width="26.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Type</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Description</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Responsibilities</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Permissions</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Systems</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Channel</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>ACT-001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Cardholder</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Human</v>
+      </c>
+      <c r="D2" t="str">
+        <v>The retail customer whose card was charged.</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Raises the dispute; supplies evidence; accepts the outcome</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Read own transactions; create dispute; attach evidence</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Mobile app; internet banking</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Mobile</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>ACT-002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Disputes agent</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Human</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Back-office analyst who investigates the case against the scheme rules.</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Reviews evidence; decides the outcome; raises the chargeback</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Read all disputes; change status; post adjustments</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Disputes console; card management system</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Back Office</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>ACT-003</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Card scheme</v>
+      </c>
+      <c r="C4" t="str">
+        <v>External</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Visa or Mastercard, which arbitrates the chargeback.</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Accepts the chargeback; rules on representment</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Receive chargeback messages</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Scheme gateway</v>
+      </c>
+      <c r="H4" t="str">
+        <v>File transfer</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>ACT-004</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Ledger</v>
+      </c>
+      <c r="C5" t="str">
+        <v>System</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Posts the provisional credit and any later reversal.</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Applies postings; guarantees a single posting per instruction</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Write postings</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Core banking</v>
+      </c>
+      <c r="H5" t="str">
+        <v>API</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H5"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M10"/>
   <cols>
     <col min="1" max="1" width="26.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -427,8 +751,314 @@
     <col min="11" max="11" width="26.83203125" customWidth="1"/>
     <col min="12" max="12" width="26.83203125" customWidth="1"/>
     <col min="13" max="13" width="26.83203125" customWidth="1"/>
-    <col min="14" max="14" width="26.83203125" customWidth="1"/>
-    <col min="15" max="15" width="26.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Flow</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Flow Name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Flow Description</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Trigger</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Outcome</v>
+      </c>
+      <c r="F1" t="str">
+        <v>SLA</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Step ID</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Step Name</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Type</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Lane</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Description</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Rules</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Next</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>PF-001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Raise and settle a card dispute</v>
+      </c>
+      <c r="C2" t="str">
+        <v>From the cardholder tapping Dispute to the case being closed.</v>
+      </c>
+      <c r="D2" t="str">
+        <v>The cardholder disputes a settled transaction</v>
+      </c>
+      <c r="E2" t="str">
+        <v>The case is Resolved or Rejected and the ledger agrees</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Provisional credit within 1 working day; outcome within 45 days</v>
+      </c>
+      <c r="G2" t="str">
+        <v>S1</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Select the transaction</v>
+      </c>
+      <c r="I2" t="str">
+        <v>start</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Cardholder</v>
+      </c>
+      <c r="K2" t="str">
+        <v>The cardholder opens a settled transaction in the app.</v>
+      </c>
+      <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2" t="str">
+        <v>S2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>PF-001</v>
+      </c>
+      <c r="G3" t="str">
+        <v>S2</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Check the dispute is allowed</v>
+      </c>
+      <c r="I3" t="str">
+        <v>decision</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Disputes service</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Status and the 120-day window are tested.</v>
+      </c>
+      <c r="L3" t="str">
+        <v>RULE-001, RULE-002</v>
+      </c>
+      <c r="M3" t="str">
+        <v>S3, S9</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>PF-001</v>
+      </c>
+      <c r="G4" t="str">
+        <v>S3</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Capture the reason code</v>
+      </c>
+      <c r="I4" t="str">
+        <v>task</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Cardholder</v>
+      </c>
+      <c r="K4" t="str">
+        <v>The cardholder picks a reason and confirms the amount.</v>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
+        <v>S4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>PF-001</v>
+      </c>
+      <c r="G5" t="str">
+        <v>S4</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Create the dispute</v>
+      </c>
+      <c r="I5" t="str">
+        <v>system</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Disputes service</v>
+      </c>
+      <c r="K5" t="str">
+        <v>The case is created with the status Submitted.</v>
+      </c>
+      <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
+        <v>S5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>PF-001</v>
+      </c>
+      <c r="G6" t="str">
+        <v>S5</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Post the provisional credit</v>
+      </c>
+      <c r="I6" t="str">
+        <v>system</v>
+      </c>
+      <c r="J6" t="str">
+        <v>Ledger</v>
+      </c>
+      <c r="K6" t="str">
+        <v>The disputed amount is credited while the case is investigated.</v>
+      </c>
+      <c r="L6" t="str">
+        <v>RULE-003</v>
+      </c>
+      <c r="M6" t="str">
+        <v>S6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>PF-001</v>
+      </c>
+      <c r="G7" t="str">
+        <v>S6</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Investigate the case</v>
+      </c>
+      <c r="I7" t="str">
+        <v>task</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Disputes agent</v>
+      </c>
+      <c r="K7" t="str">
+        <v>Evidence is read and the scheme rules applied.</v>
+      </c>
+      <c r="L7" t="str">
+        <v>RULE-004</v>
+      </c>
+      <c r="M7" t="str">
+        <v>S7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>PF-001</v>
+      </c>
+      <c r="G8" t="str">
+        <v>S7</v>
+      </c>
+      <c r="H8" t="str">
+        <v>Raise the chargeback</v>
+      </c>
+      <c r="I8" t="str">
+        <v>task</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Card scheme</v>
+      </c>
+      <c r="K8" t="str">
+        <v>The chargeback is sent to the scheme for arbitration.</v>
+      </c>
+      <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8" t="str">
+        <v>S8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>PF-001</v>
+      </c>
+      <c r="G9" t="str">
+        <v>S8</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Close the case</v>
+      </c>
+      <c r="I9" t="str">
+        <v>end</v>
+      </c>
+      <c r="J9" t="str">
+        <v>Disputes service</v>
+      </c>
+      <c r="K9" t="str">
+        <v>The case is Resolved; the provisional credit stands or is reversed.</v>
+      </c>
+      <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>PF-001</v>
+      </c>
+      <c r="G10" t="str">
+        <v>S9</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Refuse the dispute</v>
+      </c>
+      <c r="I10" t="str">
+        <v>end</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Disputes service</v>
+      </c>
+      <c r="K10" t="str">
+        <v>The cardholder is told which condition failed.</v>
+      </c>
+      <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:M10"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E4"/>
+  <cols>
+    <col min="1" max="1" width="26.83203125" customWidth="1"/>
+    <col min="2" max="2" width="26.83203125" customWidth="1"/>
+    <col min="3" max="3" width="26.83203125" customWidth="1"/>
+    <col min="4" max="4" width="26.83203125" customWidth="1"/>
+    <col min="5" max="5" width="26.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -439,241 +1069,633 @@
         <v>Title</v>
       </c>
       <c r="C1" t="str">
-        <v>Business Need</v>
+        <v>Summary</v>
       </c>
       <c r="D1" t="str">
-        <v>Description</v>
+        <v>Requirements</v>
       </c>
       <c r="E1" t="str">
-        <v>Priority</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Status</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Category</v>
-      </c>
-      <c r="H1" t="str">
-        <v>MoSCoW</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Owner</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Last Updated</v>
-      </c>
-      <c r="K1" t="str">
-        <v>Version</v>
-      </c>
-      <c r="L1" t="str">
-        <v>Rules</v>
-      </c>
-      <c r="M1" t="str">
-        <v>Tests</v>
-      </c>
-      <c r="N1" t="str">
-        <v>APIs</v>
-      </c>
-      <c r="O1" t="str">
-        <v>Documents</v>
-      </c>
-    </row>
-    <row r="2">
+        <v>Business Logic</v>
+      </c>
+    </row>
+    <row r="2" xml:space="preserve">
       <c r="A2" t="str">
+        <v>FS-001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Raising a dispute</v>
+      </c>
+      <c r="C2" t="str">
+        <v>How a dispute is created from a settled transaction: what is checked, what is stored, and what the cardholder is told at each refusal.</v>
+      </c>
+      <c r="D2" t="str">
         <v>BR-001</v>
       </c>
-      <c r="B2" t="str">
-        <v>Raise a card dispute from a settled transaction</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Disputes arrive by phone and are keyed by an agent, which costs 11 minutes per case and loses the evidence trail.</v>
-      </c>
-      <c r="D2" t="str">
-        <v>A cardholder selects a settled transaction from the last 120 days and raises a dispute against it, choosing a reason code.</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Critical</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Approved</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Disputes</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Must</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Saadaoui Abdessalem</v>
-      </c>
-      <c r="J2" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="K2" t="str">
-        <v>1.2</v>
-      </c>
-      <c r="L2" t="str">
-        <v>RULE-001, RULE-002</v>
-      </c>
-      <c r="M2" t="str">
-        <v>TC-001, TC-002</v>
-      </c>
-      <c r="N2" t="str">
-        <v>API-001</v>
-      </c>
-      <c r="O2" t="str">
-        <v>DOC-001</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="E2" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Read the transaction and confirm it is settled
+2. Confirm the settlement date is within 120 days of today
+3. Confirm no open dispute already exists for it
+4. Store the dispute with the status Submitted and return its reference</v>
+      </c>
+    </row>
+    <row r="3" xml:space="preserve">
       <c r="A3" t="str">
+        <v>FS-002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Provisional credit</v>
+      </c>
+      <c r="C3" t="str">
+        <v>How the disputed amount is returned to the cardholder while the case is investigated, and how it is reversed if the dispute fails.</v>
+      </c>
+      <c r="D3" t="str">
         <v>BR-002</v>
       </c>
-      <c r="B3" t="str">
-        <v>Credit the cardholder provisionally within one working day</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Regulation requires the funds to be restored while the case is investigated; today it is manual and late.</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Once a dispute is accepted, a provisional credit for the disputed amount is posted to the cardholder account.</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Critical</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Approved</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Disputes</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Must</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Saadaoui Abdessalem</v>
-      </c>
-      <c r="J3" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="K3" t="str">
-        <v>1.1</v>
-      </c>
-      <c r="L3" t="str">
-        <v>RULE-003</v>
-      </c>
-      <c r="M3" t="str">
-        <v>TC-003</v>
-      </c>
-      <c r="N3" t="str">
-        <v>API-002</v>
-      </c>
-      <c r="O3" t="str">
-        <v>DOC-001</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="E3" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. On acceptance, queue a posting for the disputed amount
+2. Post it in the next end-of-day run
+3. On rejection, reverse the posting and notify the cardholder</v>
+      </c>
+    </row>
+    <row r="4" xml:space="preserve">
       <c r="A4" t="str">
+        <v>FS-003</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Evidence handling</v>
+      </c>
+      <c r="C4" t="str">
+        <v>What a cardholder may attach to an open case, and what is refused.</v>
+      </c>
+      <c r="D4" t="str">
         <v>BR-003</v>
       </c>
-      <c r="B4" t="str">
-        <v>Let the cardholder attach evidence to an open dispute</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Cases stall waiting for a receipt that the cardholder already has on their phone.</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Up to five files of 10 MB each may be attached to a dispute while its status is Under Review.</v>
-      </c>
-      <c r="E4" t="str">
-        <v>High</v>
-      </c>
-      <c r="F4" t="str">
-        <v>In Review</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Disputes</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Should</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Saadaoui Abdessalem</v>
-      </c>
-      <c r="J4" t="str">
-        <v>2026-02-14</v>
-      </c>
-      <c r="K4" t="str">
-        <v>0.4</v>
-      </c>
-      <c r="L4" t="str">
-        <v>RULE-004</v>
-      </c>
-      <c r="M4" t="str">
-        <v>TC-004</v>
-      </c>
-      <c r="N4" t="str">
-        <v>API-003</v>
-      </c>
-      <c r="O4" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>BR-004</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Notify the cardholder at every change of dispute status</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Two thirds of calls to the contact centre are cardholders asking where their case stands.</v>
-      </c>
-      <c r="D5" t="str">
-        <v>A notification is sent when a dispute moves to Under Review, Resolved or Rejected.</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="F5" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Notifications</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Should</v>
-      </c>
-      <c r="I5" t="str">
-        <v>Saadaoui Abdessalem</v>
-      </c>
-      <c r="J5" t="str">
-        <v>2026-02-18</v>
-      </c>
-      <c r="K5" t="str">
-        <v>0.2</v>
-      </c>
-      <c r="L5" t="str">
-        <v/>
-      </c>
-      <c r="M5" t="str">
-        <v>TC-005</v>
-      </c>
-      <c r="N5" t="str">
-        <v/>
-      </c>
-      <c r="O5" t="str">
-        <v/>
+      <c r="E4" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Accept files only while the case is Under Review
+2. Refuse a sixth file, or any file over 10 MB
+3. Store the file against the dispute, never against the transaction</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G9"/>
+  <cols>
+    <col min="1" max="1" width="26.83203125" customWidth="1"/>
+    <col min="2" max="2" width="26.83203125" customWidth="1"/>
+    <col min="3" max="3" width="26.83203125" customWidth="1"/>
+    <col min="4" max="4" width="26.83203125" customWidth="1"/>
+    <col min="5" max="5" width="26.83203125" customWidth="1"/>
+    <col min="6" max="6" width="26.83203125" customWidth="1"/>
+    <col min="7" max="7" width="26.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Section</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Type</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Length</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Mandatory</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Description</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Example</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>FS-001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>transactionId</v>
+      </c>
+      <c r="C2" t="str">
+        <v>uuid</v>
+      </c>
+      <c r="D2" t="str">
+        <v>36</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="F2" t="str">
+        <v>The settled transaction being disputed.</v>
+      </c>
+      <c r="G2" t="str">
+        <v>9f2c1b7e-4a2d-4f9a-8b31-0c5e2a7d9f10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>FS-001</v>
+      </c>
+      <c r="B3" t="str">
+        <v>reasonCode</v>
+      </c>
+      <c r="C3" t="str">
+        <v>varchar</v>
+      </c>
+      <c r="D3" t="str">
+        <v>10</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Why the cardholder disputes the charge, in scheme terms.</v>
+      </c>
+      <c r="G3" t="str">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>FS-001</v>
+      </c>
+      <c r="B4" t="str">
+        <v>amount</v>
+      </c>
+      <c r="C4" t="str">
+        <v>numeric</v>
+      </c>
+      <c r="D4" t="str">
+        <v>15,2</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="F4" t="str">
+        <v>The disputed amount; may be less than the transaction, never more.</v>
+      </c>
+      <c r="G4" t="str">
+        <v>84.50</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>FS-001</v>
+      </c>
+      <c r="B5" t="str">
+        <v>description</v>
+      </c>
+      <c r="C5" t="str">
+        <v>varchar</v>
+      </c>
+      <c r="D5" t="str">
+        <v>500</v>
+      </c>
+      <c r="E5" t="str">
+        <v>No</v>
+      </c>
+      <c r="F5" t="str">
+        <v>The cardholder's own account of what happened.</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Charged twice for one meal</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>FS-002</v>
+      </c>
+      <c r="B6" t="str">
+        <v>postingId</v>
+      </c>
+      <c r="C6" t="str">
+        <v>uuid</v>
+      </c>
+      <c r="D6" t="str">
+        <v>36</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="F6" t="str">
+        <v>The ledger posting that carries the provisional credit.</v>
+      </c>
+      <c r="G6" t="str">
+        <v>3d81c0aa-71f4-4d2e-9c6b-6f0b2b1e77a2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>FS-002</v>
+      </c>
+      <c r="B7" t="str">
+        <v>valueDate</v>
+      </c>
+      <c r="C7" t="str">
+        <v>date</v>
+      </c>
+      <c r="D7" t="str">
+        <v>10</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="F7" t="str">
+        <v>The date the credit takes effect on the account.</v>
+      </c>
+      <c r="G7" t="str">
+        <v>2026-02-11</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>FS-003</v>
+      </c>
+      <c r="B8" t="str">
+        <v>fileName</v>
+      </c>
+      <c r="C8" t="str">
+        <v>varchar</v>
+      </c>
+      <c r="D8" t="str">
+        <v>255</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="F8" t="str">
+        <v>The name of the attached evidence file.</v>
+      </c>
+      <c r="G8" t="str">
+        <v>receipt-2026-02-08.pdf</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>FS-003</v>
+      </c>
+      <c r="B9" t="str">
+        <v>sizeBytes</v>
+      </c>
+      <c r="C9" t="str">
+        <v>bigint</v>
+      </c>
+      <c r="D9" t="str">
+        <v>—</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="F9" t="str">
+        <v>File size, checked against the 10 MB limit.</v>
+      </c>
+      <c r="G9" t="str">
+        <v>2411008</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G9"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E9"/>
+  <cols>
+    <col min="1" max="1" width="26.83203125" customWidth="1"/>
+    <col min="2" max="2" width="26.83203125" customWidth="1"/>
+    <col min="3" max="3" width="26.83203125" customWidth="1"/>
+    <col min="4" max="4" width="26.83203125" customWidth="1"/>
+    <col min="5" max="5" width="26.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Section</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Field</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Rule</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Error Code</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Severity</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>FS-001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>transactionId</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Must reference a transaction whose status is SETTLED</v>
+      </c>
+      <c r="D2" t="str">
+        <v>NOT_DISPUTABLE</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Blocking</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>FS-001</v>
+      </c>
+      <c r="B3" t="str">
+        <v>transactionId</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Settlement date must be within 120 days of today</v>
+      </c>
+      <c r="D3" t="str">
+        <v>WINDOW_CLOSED</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Blocking</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>FS-001</v>
+      </c>
+      <c r="B4" t="str">
+        <v>transactionId</v>
+      </c>
+      <c r="C4" t="str">
+        <v>No dispute may already be open against this transaction</v>
+      </c>
+      <c r="D4" t="str">
+        <v>ALREADY_DISPUTED</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Blocking</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>FS-001</v>
+      </c>
+      <c r="B5" t="str">
+        <v>amount</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Must be greater than zero and at most the transaction amount</v>
+      </c>
+      <c r="D5" t="str">
+        <v>AMOUNT_INVALID</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Blocking</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>FS-001</v>
+      </c>
+      <c r="B6" t="str">
+        <v>reasonCode</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Must be one of the scheme reason codes in force</v>
+      </c>
+      <c r="D6" t="str">
+        <v>REASON_UNKNOWN</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Blocking</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>FS-002</v>
+      </c>
+      <c r="B7" t="str">
+        <v>amount</v>
+      </c>
+      <c r="C7" t="str">
+        <v>The credit must equal the disputed amount exactly</v>
+      </c>
+      <c r="D7" t="str">
+        <v>CREDIT_MISMATCH</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Blocking</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>FS-003</v>
+      </c>
+      <c r="B8" t="str">
+        <v>sizeBytes</v>
+      </c>
+      <c r="C8" t="str">
+        <v>At most 10485760 bytes per file</v>
+      </c>
+      <c r="D8" t="str">
+        <v>ATTACHMENT_TOO_LARGE</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Blocking</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>FS-003</v>
+      </c>
+      <c r="B9" t="str">
+        <v>fileName</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Extension should be pdf, png or jpg</v>
+      </c>
+      <c r="D9" t="str">
+        <v>ATTACHMENT_TYPE</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Warning</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E9"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E8"/>
+  <cols>
+    <col min="1" max="1" width="26.83203125" customWidth="1"/>
+    <col min="2" max="2" width="26.83203125" customWidth="1"/>
+    <col min="3" max="3" width="26.83203125" customWidth="1"/>
+    <col min="4" max="4" width="26.83203125" customWidth="1"/>
+    <col min="5" max="5" width="26.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Section</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Code</v>
+      </c>
+      <c r="C1" t="str">
+        <v>HTTP Status</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Message</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Handling</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>FS-001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>NOT_DISPUTABLE</v>
+      </c>
+      <c r="C2">
+        <v>422</v>
+      </c>
+      <c r="D2" t="str">
+        <v>This transaction cannot be disputed yet.</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Tell the cardholder to wait until the payment settles, and show the date.</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>FS-001</v>
+      </c>
+      <c r="B3" t="str">
+        <v>WINDOW_CLOSED</v>
+      </c>
+      <c r="C3">
+        <v>422</v>
+      </c>
+      <c r="D3" t="str">
+        <v>The 120-day window for disputing this payment has passed.</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Show the deadline that passed and offer the contact centre.</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>FS-001</v>
+      </c>
+      <c r="B4" t="str">
+        <v>ALREADY_DISPUTED</v>
+      </c>
+      <c r="C4">
+        <v>409</v>
+      </c>
+      <c r="D4" t="str">
+        <v>There is already an open dispute for this payment.</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Take the cardholder to the existing case rather than refusing.</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>FS-001</v>
+      </c>
+      <c r="B5" t="str">
+        <v>AMOUNT_INVALID</v>
+      </c>
+      <c r="C5">
+        <v>400</v>
+      </c>
+      <c r="D5" t="str">
+        <v>The disputed amount is not valid.</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Reset the field to the full transaction amount.</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>FS-002</v>
+      </c>
+      <c r="B6" t="str">
+        <v>CREDIT_MISMATCH</v>
+      </c>
+      <c r="C6">
+        <v>500</v>
+      </c>
+      <c r="D6" t="str">
+        <v>The provisional credit does not match the disputed amount.</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Hold the posting and raise an operations alert; never post a partial credit.</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>FS-003</v>
+      </c>
+      <c r="B7" t="str">
+        <v>ATTACHMENT_LIMIT</v>
+      </c>
+      <c r="C7">
+        <v>422</v>
+      </c>
+      <c r="D7" t="str">
+        <v>You can attach up to five files.</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Hide the attach action once five files exist, rather than failing on the sixth.</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>FS-003</v>
+      </c>
+      <c r="B8" t="str">
+        <v>ATTACHMENT_TOO_LARGE</v>
+      </c>
+      <c r="C8">
+        <v>413</v>
+      </c>
+      <c r="D8" t="str">
+        <v>That file is larger than 10 MB.</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Say the limit before the upload starts, not after it finishes.</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E8"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D7"/>
   <cols>
@@ -788,7 +1810,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I6"/>
   <cols>
@@ -1092,7 +2114,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K4"/>
   <cols>
@@ -1256,7 +2278,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K5"/>
   <cols>
@@ -1455,7 +2477,86 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B8"/>
+  <cols>
+    <col min="1" max="1" width="26.83203125" customWidth="1"/>
+    <col min="2" max="2" width="26.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Item</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>In</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Raising a dispute from a settled card transaction</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>In</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Provisional credit and its reversal</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>In</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Evidence upload while the case is under review</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>In</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Chargeback submission to the scheme</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Out</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Merchant-side representment handling</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Out</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Fraud case management (separate programme)</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Out</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Cash and cheque disputes</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B8"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L4"/>
   <cols>
@@ -1647,7 +2748,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <cols>
@@ -1909,7 +3010,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L4"/>
   <cols>
@@ -2086,7 +3187,727 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F6"/>
+  <cols>
+    <col min="1" max="1" width="26.83203125" customWidth="1"/>
+    <col min="2" max="2" width="26.83203125" customWidth="1"/>
+    <col min="3" max="3" width="26.83203125" customWidth="1"/>
+    <col min="4" max="4" width="26.83203125" customWidth="1"/>
+    <col min="5" max="5" width="26.83203125" customWidth="1"/>
+    <col min="6" max="6" width="26.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Role</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Email</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Department</v>
+      </c>
+      <c r="F1" t="str">
+        <v>RACI</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>STK-001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Head of Card Operations</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Business Owner</v>
+      </c>
+      <c r="D2" t="str">
+        <v>card.ops@bank.example</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Card Operations</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Accountable</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>STK-002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Saadaoui Abdessalem</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Lead Functional Analyst</v>
+      </c>
+      <c r="D3" t="str">
+        <v>abdessalemsaa@gmail.com</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Change Delivery</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Responsible</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>STK-003</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Disputes Team Lead</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Process Owner</v>
+      </c>
+      <c r="D4" t="str">
+        <v>disputes@bank.example</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Card Operations</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Consulted</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>STK-004</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Compliance Officer</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Regulatory Assurance</v>
+      </c>
+      <c r="D5" t="str">
+        <v>compliance@bank.example</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Compliance</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Consulted</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>STK-005</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Head of Internal Audit</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Assurance</v>
+      </c>
+      <c r="D6" t="str">
+        <v>audit@bank.example</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Internal Audit</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Informed</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E6"/>
+  <cols>
+    <col min="1" max="1" width="26.83203125" customWidth="1"/>
+    <col min="2" max="2" width="26.83203125" customWidth="1"/>
+    <col min="3" max="3" width="26.83203125" customWidth="1"/>
+    <col min="4" max="4" width="26.83203125" customWidth="1"/>
+    <col min="5" max="5" width="26.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Label</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Date</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Status</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Description</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>MS-01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Business case approved</v>
+      </c>
+      <c r="C2" t="str">
+        <v>2026-01-05</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Cards steering committee approved the investment.</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>MS-02</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Requirements baselined</v>
+      </c>
+      <c r="C3" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Four requirements signed off with Operations and Compliance.</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>MS-03</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Functional specification approved</v>
+      </c>
+      <c r="C4" t="str">
+        <v>2026-03-06</v>
+      </c>
+      <c r="D4" t="str">
+        <v>In Progress</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Field tables and error codes under review.</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>MS-04</v>
+      </c>
+      <c r="B5" t="str">
+        <v>SIT and UAT</v>
+      </c>
+      <c r="C5" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Upcoming</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Five test cases, two suites.</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>MS-05</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Go-live</v>
+      </c>
+      <c r="C6" t="str">
+        <v>2026-06-30</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Upcoming</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Pilot cohort first, then full rollout.</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F4"/>
+  <cols>
+    <col min="1" max="1" width="26.83203125" customWidth="1"/>
+    <col min="2" max="2" width="26.83203125" customWidth="1"/>
+    <col min="3" max="3" width="26.83203125" customWidth="1"/>
+    <col min="4" max="4" width="26.83203125" customWidth="1"/>
+    <col min="5" max="5" width="26.83203125" customWidth="1"/>
+    <col min="6" max="6" width="26.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Type</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Owner</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Status</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Description</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>DEP-01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Card scheme gateway</v>
+      </c>
+      <c r="C2" t="str">
+        <v>External Party</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Integration Team</v>
+      </c>
+      <c r="E2" t="str">
+        <v>On Track</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Chargeback submission and arbitration messages.</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>DEP-02</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Core banking ledger</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Internal System</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Core Banking</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Resolved</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Posting API for the provisional credit and its reversal.</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>DEP-03</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Document store</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Vendor</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Platform Team</v>
+      </c>
+      <c r="E4" t="str">
+        <v>At Risk</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Evidence files; the 10 MB limit is not yet enforced server-side.</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F4"/>
+  <cols>
+    <col min="1" max="1" width="26.83203125" customWidth="1"/>
+    <col min="2" max="2" width="26.83203125" customWidth="1"/>
+    <col min="3" max="3" width="26.83203125" customWidth="1"/>
+    <col min="4" max="4" width="26.83203125" customWidth="1"/>
+    <col min="5" max="5" width="26.83203125" customWidth="1"/>
+    <col min="6" max="6" width="26.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Description</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Likelihood</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Impact</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Mitigation</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Owner</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>R-01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>The provisional credit posts twice if the end-of-day run is replayed.</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="D2" t="str">
+        <v>High</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Idempotency key on the posting instruction, checked by SQL-002.</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Saadaoui Abdessalem</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>R-02</v>
+      </c>
+      <c r="B3" t="str">
+        <v>The attachment limit is enforced only in the app, not the API.</v>
+      </c>
+      <c r="C3" t="str">
+        <v>High</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Move the check server-side before the March release; tracked by DEF-118.</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Saadaoui Abdessalem</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>R-03</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Scheme rule changes in chapter 11 could shorten the dispute window.</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Low</v>
+      </c>
+      <c r="D4" t="str">
+        <v>High</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Window held in configuration, not code.</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Compliance Officer</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:O5"/>
+  <cols>
+    <col min="1" max="1" width="26.83203125" customWidth="1"/>
+    <col min="2" max="2" width="26.83203125" customWidth="1"/>
+    <col min="3" max="3" width="26.83203125" customWidth="1"/>
+    <col min="4" max="4" width="26.83203125" customWidth="1"/>
+    <col min="5" max="5" width="26.83203125" customWidth="1"/>
+    <col min="6" max="6" width="26.83203125" customWidth="1"/>
+    <col min="7" max="7" width="26.83203125" customWidth="1"/>
+    <col min="8" max="8" width="26.83203125" customWidth="1"/>
+    <col min="9" max="9" width="26.83203125" customWidth="1"/>
+    <col min="10" max="10" width="26.83203125" customWidth="1"/>
+    <col min="11" max="11" width="26.83203125" customWidth="1"/>
+    <col min="12" max="12" width="26.83203125" customWidth="1"/>
+    <col min="13" max="13" width="26.83203125" customWidth="1"/>
+    <col min="14" max="14" width="26.83203125" customWidth="1"/>
+    <col min="15" max="15" width="26.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Title</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Business Need</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Description</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Priority</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Status</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Category</v>
+      </c>
+      <c r="H1" t="str">
+        <v>MoSCoW</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Owner</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Last Updated</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Version</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Rules</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Tests</v>
+      </c>
+      <c r="N1" t="str">
+        <v>APIs</v>
+      </c>
+      <c r="O1" t="str">
+        <v>Documents</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>BR-001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Raise a card dispute from a settled transaction</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Disputes arrive by phone and are keyed by an agent, which costs 11 minutes per case and loses the evidence trail.</v>
+      </c>
+      <c r="D2" t="str">
+        <v>A cardholder selects a settled transaction from the last 120 days and raises a dispute against it, choosing a reason code.</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Approved</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Disputes</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Must</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Saadaoui Abdessalem</v>
+      </c>
+      <c r="J2" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="K2" t="str">
+        <v>1.2</v>
+      </c>
+      <c r="L2" t="str">
+        <v>RULE-001, RULE-002</v>
+      </c>
+      <c r="M2" t="str">
+        <v>TC-001, TC-002</v>
+      </c>
+      <c r="N2" t="str">
+        <v>API-001</v>
+      </c>
+      <c r="O2" t="str">
+        <v>DOC-001</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>BR-002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Credit the cardholder provisionally within one working day</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Regulation requires the funds to be restored while the case is investigated; today it is manual and late.</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Once a dispute is accepted, a provisional credit for the disputed amount is posted to the cardholder account.</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Approved</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Disputes</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Must</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Saadaoui Abdessalem</v>
+      </c>
+      <c r="J3" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="K3" t="str">
+        <v>1.1</v>
+      </c>
+      <c r="L3" t="str">
+        <v>RULE-003</v>
+      </c>
+      <c r="M3" t="str">
+        <v>TC-003</v>
+      </c>
+      <c r="N3" t="str">
+        <v>API-002</v>
+      </c>
+      <c r="O3" t="str">
+        <v>DOC-001</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>BR-003</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Let the cardholder attach evidence to an open dispute</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Cases stall waiting for a receipt that the cardholder already has on their phone.</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Up to five files of 10 MB each may be attached to a dispute while its status is Under Review.</v>
+      </c>
+      <c r="E4" t="str">
+        <v>High</v>
+      </c>
+      <c r="F4" t="str">
+        <v>In Review</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Disputes</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Should</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Saadaoui Abdessalem</v>
+      </c>
+      <c r="J4" t="str">
+        <v>2026-02-14</v>
+      </c>
+      <c r="K4" t="str">
+        <v>0.4</v>
+      </c>
+      <c r="L4" t="str">
+        <v>RULE-004</v>
+      </c>
+      <c r="M4" t="str">
+        <v>TC-004</v>
+      </c>
+      <c r="N4" t="str">
+        <v>API-003</v>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>BR-004</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Notify the cardholder at every change of dispute status</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Two thirds of calls to the contact centre are cardholders asking where their case stands.</v>
+      </c>
+      <c r="D5" t="str">
+        <v>A notification is sent when a dispute moves to Under Review, Resolved or Rejected.</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Notifications</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Should</v>
+      </c>
+      <c r="I5" t="str">
+        <v>Saadaoui Abdessalem</v>
+      </c>
+      <c r="J5" t="str">
+        <v>2026-02-18</v>
+      </c>
+      <c r="K5" t="str">
+        <v>0.2</v>
+      </c>
+      <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
+        <v>TC-005</v>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:O5"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E8"/>
   <cols>
@@ -2240,7 +4061,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J5"/>
   <cols>
@@ -2421,1116 +4242,4 @@
     <ignoredError numberStoredAsText="1" sqref="A1:J5"/>
   </ignoredErrors>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
-  <cols>
-    <col min="1" max="1" width="26.83203125" customWidth="1"/>
-    <col min="2" max="2" width="26.83203125" customWidth="1"/>
-    <col min="3" max="3" width="26.83203125" customWidth="1"/>
-    <col min="4" max="4" width="26.83203125" customWidth="1"/>
-    <col min="5" max="5" width="26.83203125" customWidth="1"/>
-    <col min="6" max="6" width="26.83203125" customWidth="1"/>
-    <col min="7" max="7" width="26.83203125" customWidth="1"/>
-    <col min="8" max="8" width="26.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>ID</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Name</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Type</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Description</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Responsibilities</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Permissions</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Systems</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Channel</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>ACT-001</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Cardholder</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Human</v>
-      </c>
-      <c r="D2" t="str">
-        <v>The retail customer whose card was charged.</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Raises the dispute; supplies evidence; accepts the outcome</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Read own transactions; create dispute; attach evidence</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Mobile app; internet banking</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Mobile</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>ACT-002</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Disputes agent</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Human</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Back-office analyst who investigates the case against the scheme rules.</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Reviews evidence; decides the outcome; raises the chargeback</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Read all disputes; change status; post adjustments</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Disputes console; card management system</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Back Office</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>ACT-003</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Card scheme</v>
-      </c>
-      <c r="C4" t="str">
-        <v>External</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Visa or Mastercard, which arbitrates the chargeback.</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Accepts the chargeback; rules on representment</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Receive chargeback messages</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Scheme gateway</v>
-      </c>
-      <c r="H4" t="str">
-        <v>File transfer</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>ACT-004</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Ledger</v>
-      </c>
-      <c r="C5" t="str">
-        <v>System</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Posts the provisional credit and any later reversal.</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Applies postings; guarantees a single posting per instruction</v>
-      </c>
-      <c r="F5" t="str">
-        <v>Write postings</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Core banking</v>
-      </c>
-      <c r="H5" t="str">
-        <v>API</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H5"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
-  <cols>
-    <col min="1" max="1" width="26.83203125" customWidth="1"/>
-    <col min="2" max="2" width="26.83203125" customWidth="1"/>
-    <col min="3" max="3" width="26.83203125" customWidth="1"/>
-    <col min="4" max="4" width="26.83203125" customWidth="1"/>
-    <col min="5" max="5" width="26.83203125" customWidth="1"/>
-    <col min="6" max="6" width="26.83203125" customWidth="1"/>
-    <col min="7" max="7" width="26.83203125" customWidth="1"/>
-    <col min="8" max="8" width="26.83203125" customWidth="1"/>
-    <col min="9" max="9" width="26.83203125" customWidth="1"/>
-    <col min="10" max="10" width="26.83203125" customWidth="1"/>
-    <col min="11" max="11" width="26.83203125" customWidth="1"/>
-    <col min="12" max="12" width="26.83203125" customWidth="1"/>
-    <col min="13" max="13" width="26.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Flow</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Flow Name</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Flow Description</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Trigger</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Outcome</v>
-      </c>
-      <c r="F1" t="str">
-        <v>SLA</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Step ID</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Step Name</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Type</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Lane</v>
-      </c>
-      <c r="K1" t="str">
-        <v>Description</v>
-      </c>
-      <c r="L1" t="str">
-        <v>Rules</v>
-      </c>
-      <c r="M1" t="str">
-        <v>Next</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>PF-001</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Raise and settle a card dispute</v>
-      </c>
-      <c r="C2" t="str">
-        <v>From the cardholder tapping Dispute to the case being closed.</v>
-      </c>
-      <c r="D2" t="str">
-        <v>The cardholder disputes a settled transaction</v>
-      </c>
-      <c r="E2" t="str">
-        <v>The case is Resolved or Rejected and the ledger agrees</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Provisional credit within 1 working day; outcome within 45 days</v>
-      </c>
-      <c r="G2" t="str">
-        <v>S1</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Select the transaction</v>
-      </c>
-      <c r="I2" t="str">
-        <v>start</v>
-      </c>
-      <c r="J2" t="str">
-        <v>Cardholder</v>
-      </c>
-      <c r="K2" t="str">
-        <v>The cardholder opens a settled transaction in the app.</v>
-      </c>
-      <c r="L2" t="str">
-        <v/>
-      </c>
-      <c r="M2" t="str">
-        <v>S2</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>PF-001</v>
-      </c>
-      <c r="G3" t="str">
-        <v>S2</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Check the dispute is allowed</v>
-      </c>
-      <c r="I3" t="str">
-        <v>decision</v>
-      </c>
-      <c r="J3" t="str">
-        <v>Disputes service</v>
-      </c>
-      <c r="K3" t="str">
-        <v>Status and the 120-day window are tested.</v>
-      </c>
-      <c r="L3" t="str">
-        <v>RULE-001, RULE-002</v>
-      </c>
-      <c r="M3" t="str">
-        <v>S3, S9</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>PF-001</v>
-      </c>
-      <c r="G4" t="str">
-        <v>S3</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Capture the reason code</v>
-      </c>
-      <c r="I4" t="str">
-        <v>task</v>
-      </c>
-      <c r="J4" t="str">
-        <v>Cardholder</v>
-      </c>
-      <c r="K4" t="str">
-        <v>The cardholder picks a reason and confirms the amount.</v>
-      </c>
-      <c r="L4" t="str">
-        <v/>
-      </c>
-      <c r="M4" t="str">
-        <v>S4</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>PF-001</v>
-      </c>
-      <c r="G5" t="str">
-        <v>S4</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Create the dispute</v>
-      </c>
-      <c r="I5" t="str">
-        <v>system</v>
-      </c>
-      <c r="J5" t="str">
-        <v>Disputes service</v>
-      </c>
-      <c r="K5" t="str">
-        <v>The case is created with the status Submitted.</v>
-      </c>
-      <c r="L5" t="str">
-        <v/>
-      </c>
-      <c r="M5" t="str">
-        <v>S5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>PF-001</v>
-      </c>
-      <c r="G6" t="str">
-        <v>S5</v>
-      </c>
-      <c r="H6" t="str">
-        <v>Post the provisional credit</v>
-      </c>
-      <c r="I6" t="str">
-        <v>system</v>
-      </c>
-      <c r="J6" t="str">
-        <v>Ledger</v>
-      </c>
-      <c r="K6" t="str">
-        <v>The disputed amount is credited while the case is investigated.</v>
-      </c>
-      <c r="L6" t="str">
-        <v>RULE-003</v>
-      </c>
-      <c r="M6" t="str">
-        <v>S6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>PF-001</v>
-      </c>
-      <c r="G7" t="str">
-        <v>S6</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Investigate the case</v>
-      </c>
-      <c r="I7" t="str">
-        <v>task</v>
-      </c>
-      <c r="J7" t="str">
-        <v>Disputes agent</v>
-      </c>
-      <c r="K7" t="str">
-        <v>Evidence is read and the scheme rules applied.</v>
-      </c>
-      <c r="L7" t="str">
-        <v>RULE-004</v>
-      </c>
-      <c r="M7" t="str">
-        <v>S7</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>PF-001</v>
-      </c>
-      <c r="G8" t="str">
-        <v>S7</v>
-      </c>
-      <c r="H8" t="str">
-        <v>Raise the chargeback</v>
-      </c>
-      <c r="I8" t="str">
-        <v>task</v>
-      </c>
-      <c r="J8" t="str">
-        <v>Card scheme</v>
-      </c>
-      <c r="K8" t="str">
-        <v>The chargeback is sent to the scheme for arbitration.</v>
-      </c>
-      <c r="L8" t="str">
-        <v/>
-      </c>
-      <c r="M8" t="str">
-        <v>S8</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>PF-001</v>
-      </c>
-      <c r="G9" t="str">
-        <v>S8</v>
-      </c>
-      <c r="H9" t="str">
-        <v>Close the case</v>
-      </c>
-      <c r="I9" t="str">
-        <v>end</v>
-      </c>
-      <c r="J9" t="str">
-        <v>Disputes service</v>
-      </c>
-      <c r="K9" t="str">
-        <v>The case is Resolved; the provisional credit stands or is reversed.</v>
-      </c>
-      <c r="L9" t="str">
-        <v/>
-      </c>
-      <c r="M9" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>PF-001</v>
-      </c>
-      <c r="G10" t="str">
-        <v>S9</v>
-      </c>
-      <c r="H10" t="str">
-        <v>Refuse the dispute</v>
-      </c>
-      <c r="I10" t="str">
-        <v>end</v>
-      </c>
-      <c r="J10" t="str">
-        <v>Disputes service</v>
-      </c>
-      <c r="K10" t="str">
-        <v>The cardholder is told which condition failed.</v>
-      </c>
-      <c r="L10" t="str">
-        <v/>
-      </c>
-      <c r="M10" t="str">
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M10"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
-  <cols>
-    <col min="1" max="1" width="26.83203125" customWidth="1"/>
-    <col min="2" max="2" width="26.83203125" customWidth="1"/>
-    <col min="3" max="3" width="26.83203125" customWidth="1"/>
-    <col min="4" max="4" width="26.83203125" customWidth="1"/>
-    <col min="5" max="5" width="26.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>ID</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Title</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Summary</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Requirements</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Business Logic</v>
-      </c>
-    </row>
-    <row r="2" xml:space="preserve">
-      <c r="A2" t="str">
-        <v>FS-001</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Raising a dispute</v>
-      </c>
-      <c r="C2" t="str">
-        <v>How a dispute is created from a settled transaction: what is checked, what is stored, and what the cardholder is told at each refusal.</v>
-      </c>
-      <c r="D2" t="str">
-        <v>BR-001</v>
-      </c>
-      <c r="E2" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Read the transaction and confirm it is settled
-2. Confirm the settlement date is within 120 days of today
-3. Confirm no open dispute already exists for it
-4. Store the dispute with the status Submitted and return its reference</v>
-      </c>
-    </row>
-    <row r="3" xml:space="preserve">
-      <c r="A3" t="str">
-        <v>FS-002</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Provisional credit</v>
-      </c>
-      <c r="C3" t="str">
-        <v>How the disputed amount is returned to the cardholder while the case is investigated, and how it is reversed if the dispute fails.</v>
-      </c>
-      <c r="D3" t="str">
-        <v>BR-002</v>
-      </c>
-      <c r="E3" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. On acceptance, queue a posting for the disputed amount
-2. Post it in the next end-of-day run
-3. On rejection, reverse the posting and notify the cardholder</v>
-      </c>
-    </row>
-    <row r="4" xml:space="preserve">
-      <c r="A4" t="str">
-        <v>FS-003</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Evidence handling</v>
-      </c>
-      <c r="C4" t="str">
-        <v>What a cardholder may attach to an open case, and what is refused.</v>
-      </c>
-      <c r="D4" t="str">
-        <v>BR-003</v>
-      </c>
-      <c r="E4" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Accept files only while the case is Under Review
-2. Refuse a sixth file, or any file over 10 MB
-3. Store the file against the dispute, never against the transaction</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E4"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
-  <cols>
-    <col min="1" max="1" width="26.83203125" customWidth="1"/>
-    <col min="2" max="2" width="26.83203125" customWidth="1"/>
-    <col min="3" max="3" width="26.83203125" customWidth="1"/>
-    <col min="4" max="4" width="26.83203125" customWidth="1"/>
-    <col min="5" max="5" width="26.83203125" customWidth="1"/>
-    <col min="6" max="6" width="26.83203125" customWidth="1"/>
-    <col min="7" max="7" width="26.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Section</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Name</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Type</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Length</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Mandatory</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Description</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Example</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>FS-001</v>
-      </c>
-      <c r="B2" t="str">
-        <v>transactionId</v>
-      </c>
-      <c r="C2" t="str">
-        <v>uuid</v>
-      </c>
-      <c r="D2" t="str">
-        <v>36</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="F2" t="str">
-        <v>The settled transaction being disputed.</v>
-      </c>
-      <c r="G2" t="str">
-        <v>9f2c1b7e-4a2d-4f9a-8b31-0c5e2a7d9f10</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>FS-001</v>
-      </c>
-      <c r="B3" t="str">
-        <v>reasonCode</v>
-      </c>
-      <c r="C3" t="str">
-        <v>varchar</v>
-      </c>
-      <c r="D3" t="str">
-        <v>10</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Why the cardholder disputes the charge, in scheme terms.</v>
-      </c>
-      <c r="G3" t="str">
-        <v>13.1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>FS-001</v>
-      </c>
-      <c r="B4" t="str">
-        <v>amount</v>
-      </c>
-      <c r="C4" t="str">
-        <v>numeric</v>
-      </c>
-      <c r="D4" t="str">
-        <v>15,2</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="F4" t="str">
-        <v>The disputed amount; may be less than the transaction, never more.</v>
-      </c>
-      <c r="G4" t="str">
-        <v>84.50</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>FS-001</v>
-      </c>
-      <c r="B5" t="str">
-        <v>description</v>
-      </c>
-      <c r="C5" t="str">
-        <v>varchar</v>
-      </c>
-      <c r="D5" t="str">
-        <v>500</v>
-      </c>
-      <c r="E5" t="str">
-        <v>No</v>
-      </c>
-      <c r="F5" t="str">
-        <v>The cardholder's own account of what happened.</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Charged twice for one meal</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>FS-002</v>
-      </c>
-      <c r="B6" t="str">
-        <v>postingId</v>
-      </c>
-      <c r="C6" t="str">
-        <v>uuid</v>
-      </c>
-      <c r="D6" t="str">
-        <v>36</v>
-      </c>
-      <c r="E6" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="F6" t="str">
-        <v>The ledger posting that carries the provisional credit.</v>
-      </c>
-      <c r="G6" t="str">
-        <v>3d81c0aa-71f4-4d2e-9c6b-6f0b2b1e77a2</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>FS-002</v>
-      </c>
-      <c r="B7" t="str">
-        <v>valueDate</v>
-      </c>
-      <c r="C7" t="str">
-        <v>date</v>
-      </c>
-      <c r="D7" t="str">
-        <v>10</v>
-      </c>
-      <c r="E7" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="F7" t="str">
-        <v>The date the credit takes effect on the account.</v>
-      </c>
-      <c r="G7" t="str">
-        <v>2026-02-11</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>FS-003</v>
-      </c>
-      <c r="B8" t="str">
-        <v>fileName</v>
-      </c>
-      <c r="C8" t="str">
-        <v>varchar</v>
-      </c>
-      <c r="D8" t="str">
-        <v>255</v>
-      </c>
-      <c r="E8" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="F8" t="str">
-        <v>The name of the attached evidence file.</v>
-      </c>
-      <c r="G8" t="str">
-        <v>receipt-2026-02-08.pdf</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>FS-003</v>
-      </c>
-      <c r="B9" t="str">
-        <v>sizeBytes</v>
-      </c>
-      <c r="C9" t="str">
-        <v>bigint</v>
-      </c>
-      <c r="D9" t="str">
-        <v>—</v>
-      </c>
-      <c r="E9" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="F9" t="str">
-        <v>File size, checked against the 10 MB limit.</v>
-      </c>
-      <c r="G9" t="str">
-        <v>2411008</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G9"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E9"/>
-  <cols>
-    <col min="1" max="1" width="26.83203125" customWidth="1"/>
-    <col min="2" max="2" width="26.83203125" customWidth="1"/>
-    <col min="3" max="3" width="26.83203125" customWidth="1"/>
-    <col min="4" max="4" width="26.83203125" customWidth="1"/>
-    <col min="5" max="5" width="26.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Section</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Field</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Rule</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Error Code</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Severity</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>FS-001</v>
-      </c>
-      <c r="B2" t="str">
-        <v>transactionId</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Must reference a transaction whose status is SETTLED</v>
-      </c>
-      <c r="D2" t="str">
-        <v>NOT_DISPUTABLE</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Blocking</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>FS-001</v>
-      </c>
-      <c r="B3" t="str">
-        <v>transactionId</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Settlement date must be within 120 days of today</v>
-      </c>
-      <c r="D3" t="str">
-        <v>WINDOW_CLOSED</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Blocking</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>FS-001</v>
-      </c>
-      <c r="B4" t="str">
-        <v>transactionId</v>
-      </c>
-      <c r="C4" t="str">
-        <v>No dispute may already be open against this transaction</v>
-      </c>
-      <c r="D4" t="str">
-        <v>ALREADY_DISPUTED</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Blocking</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>FS-001</v>
-      </c>
-      <c r="B5" t="str">
-        <v>amount</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Must be greater than zero and at most the transaction amount</v>
-      </c>
-      <c r="D5" t="str">
-        <v>AMOUNT_INVALID</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Blocking</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>FS-001</v>
-      </c>
-      <c r="B6" t="str">
-        <v>reasonCode</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Must be one of the scheme reason codes in force</v>
-      </c>
-      <c r="D6" t="str">
-        <v>REASON_UNKNOWN</v>
-      </c>
-      <c r="E6" t="str">
-        <v>Blocking</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>FS-002</v>
-      </c>
-      <c r="B7" t="str">
-        <v>amount</v>
-      </c>
-      <c r="C7" t="str">
-        <v>The credit must equal the disputed amount exactly</v>
-      </c>
-      <c r="D7" t="str">
-        <v>CREDIT_MISMATCH</v>
-      </c>
-      <c r="E7" t="str">
-        <v>Blocking</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>FS-003</v>
-      </c>
-      <c r="B8" t="str">
-        <v>sizeBytes</v>
-      </c>
-      <c r="C8" t="str">
-        <v>At most 10485760 bytes per file</v>
-      </c>
-      <c r="D8" t="str">
-        <v>ATTACHMENT_TOO_LARGE</v>
-      </c>
-      <c r="E8" t="str">
-        <v>Blocking</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>FS-003</v>
-      </c>
-      <c r="B9" t="str">
-        <v>fileName</v>
-      </c>
-      <c r="C9" t="str">
-        <v>Extension should be pdf, png or jpg</v>
-      </c>
-      <c r="D9" t="str">
-        <v>ATTACHMENT_TYPE</v>
-      </c>
-      <c r="E9" t="str">
-        <v>Warning</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E9"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E8"/>
-  <cols>
-    <col min="1" max="1" width="26.83203125" customWidth="1"/>
-    <col min="2" max="2" width="26.83203125" customWidth="1"/>
-    <col min="3" max="3" width="26.83203125" customWidth="1"/>
-    <col min="4" max="4" width="26.83203125" customWidth="1"/>
-    <col min="5" max="5" width="26.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Section</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Code</v>
-      </c>
-      <c r="C1" t="str">
-        <v>HTTP Status</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Message</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Handling</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>FS-001</v>
-      </c>
-      <c r="B2" t="str">
-        <v>NOT_DISPUTABLE</v>
-      </c>
-      <c r="C2">
-        <v>422</v>
-      </c>
-      <c r="D2" t="str">
-        <v>This transaction cannot be disputed yet.</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Tell the cardholder to wait until the payment settles, and show the date.</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>FS-001</v>
-      </c>
-      <c r="B3" t="str">
-        <v>WINDOW_CLOSED</v>
-      </c>
-      <c r="C3">
-        <v>422</v>
-      </c>
-      <c r="D3" t="str">
-        <v>The 120-day window for disputing this payment has passed.</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Show the deadline that passed and offer the contact centre.</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>FS-001</v>
-      </c>
-      <c r="B4" t="str">
-        <v>ALREADY_DISPUTED</v>
-      </c>
-      <c r="C4">
-        <v>409</v>
-      </c>
-      <c r="D4" t="str">
-        <v>There is already an open dispute for this payment.</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Take the cardholder to the existing case rather than refusing.</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>FS-001</v>
-      </c>
-      <c r="B5" t="str">
-        <v>AMOUNT_INVALID</v>
-      </c>
-      <c r="C5">
-        <v>400</v>
-      </c>
-      <c r="D5" t="str">
-        <v>The disputed amount is not valid.</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Reset the field to the full transaction amount.</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>FS-002</v>
-      </c>
-      <c r="B6" t="str">
-        <v>CREDIT_MISMATCH</v>
-      </c>
-      <c r="C6">
-        <v>500</v>
-      </c>
-      <c r="D6" t="str">
-        <v>The provisional credit does not match the disputed amount.</v>
-      </c>
-      <c r="E6" t="str">
-        <v>Hold the posting and raise an operations alert; never post a partial credit.</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>FS-003</v>
-      </c>
-      <c r="B7" t="str">
-        <v>ATTACHMENT_LIMIT</v>
-      </c>
-      <c r="C7">
-        <v>422</v>
-      </c>
-      <c r="D7" t="str">
-        <v>You can attach up to five files.</v>
-      </c>
-      <c r="E7" t="str">
-        <v>Hide the attach action once five files exist, rather than failing on the sixth.</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>FS-003</v>
-      </c>
-      <c r="B8" t="str">
-        <v>ATTACHMENT_TOO_LARGE</v>
-      </c>
-      <c r="C8">
-        <v>413</v>
-      </c>
-      <c r="D8" t="str">
-        <v>That file is larger than 10 MB.</v>
-      </c>
-      <c r="E8" t="str">
-        <v>Say the limit before the upload starts, not after it finishes.</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E8"/>
-  </ignoredErrors>
-</worksheet>
 </file>
--- a/public/fa/example-project.xlsx
+++ b/public/fa/example-project.xlsx
@@ -418,7 +418,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <cols>
     <col min="1" max="1" width="26.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -576,9 +576,17 @@
         <v>Cards, Disputes, Automation</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Stack</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Java, Spring Boot, PostgreSQL, Swagger, Postman, Docker</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B20"/>
   </ignoredErrors>
 </worksheet>
 </file>
